--- a/research/traditional_assets/database/data/bahrain/bahrain_retail_distributors.xlsx
+++ b/research/traditional_assets/database/data/bahrain/bahrain_retail_distributors.xlsx
@@ -1133,43 +1133,43 @@
         <v>5.74285714285714</v>
       </c>
       <c r="F2">
-        <v>10000000</v>
+        <v>186.329982066636</v>
       </c>
       <c r="G2">
         <v>1.80141843971631</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.0782269503546099</v>
       </c>
       <c r="I2">
         <v>0.230281051677244</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K2">
         <v>169.8</v>
       </c>
       <c r="L2">
-        <v>262.905665928035</v>
+        <v>260.54974545799</v>
       </c>
       <c r="M2">
         <v>205.1</v>
       </c>
       <c r="N2">
-        <v>247.405665928035</v>
+        <v>247.25574545799</v>
       </c>
       <c r="O2">
         <v>50.8</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>2.206</v>
       </c>
       <c r="Q2">
         <v>0.12865733137653</v>
       </c>
       <c r="R2">
-        <v>0.113348894565893</v>
+        <v>0.113393894565893</v>
       </c>
       <c r="S2">
         <v>0.112277188197372</v>
@@ -1191,13 +1191,13 @@
         <v>0.133557868911873</v>
       </c>
       <c r="X2">
-        <v>0.113348894565893</v>
+        <v>0.114031206632215</v>
       </c>
       <c r="Y2">
         <v>0.751714925427003</v>
       </c>
       <c r="Z2">
-        <v>0.578609221838192</v>
+        <v>0.584453759432517</v>
       </c>
       <c r="AA2">
         <v>50.8</v>
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1133488945658929</v>
+        <v>0.1133938945658929</v>
       </c>
       <c r="C2">
-        <v>262.9056659280352</v>
+        <v>260.5497454579904</v>
       </c>
       <c r="D2">
-        <v>247.4056659280352</v>
+        <v>247.2557454579904</v>
       </c>
       <c r="E2">
-        <v>-50.8</v>
+        <v>-48.59399999999999</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2.206</v>
       </c>
       <c r="G2">
         <v>15.5</v>
@@ -1451,28 +1451,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1109618</v>
       </c>
       <c r="N2">
-        <v>20.67551020408164</v>
+        <v>20.56454840408164</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>20.67551020408164</v>
+        <v>20.56454840408164</v>
       </c>
       <c r="Q2">
-        <v>28.77551020408163</v>
+        <v>28.66454840408164</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1133488945658929</v>
+        <v>0.1140312066322151</v>
       </c>
       <c r="T2">
-        <v>0.5786092218381922</v>
+        <v>0.5844537594325174</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>186.3299820666359</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1133938945658929</v>
+        <v>0.1134388945658929</v>
       </c>
       <c r="C3">
-        <v>260.5497454579904</v>
+        <v>258.1940065725964</v>
       </c>
       <c r="D3">
-        <v>247.2557454579904</v>
+        <v>247.1060065725964</v>
       </c>
       <c r="E3">
-        <v>-48.59399999999999</v>
+        <v>-46.388</v>
       </c>
       <c r="F3">
-        <v>2.206</v>
+        <v>4.412000000000001</v>
       </c>
       <c r="G3">
         <v>15.5</v>
@@ -1533,28 +1533,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M3">
-        <v>0.1109618</v>
+        <v>0.2219236</v>
       </c>
       <c r="N3">
-        <v>20.56454840408164</v>
+        <v>20.45358660408164</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>20.56454840408164</v>
+        <v>20.45358660408164</v>
       </c>
       <c r="Q3">
-        <v>28.66454840408164</v>
+        <v>28.55358660408163</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1140312066322151</v>
+        <v>0.1147274434345846</v>
       </c>
       <c r="T3">
-        <v>0.5844537594325174</v>
+        <v>0.5904175733042778</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>186.3299820666359</v>
+        <v>93.16499103331792</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1134388945658929</v>
+        <v>0.1134838945658929</v>
       </c>
       <c r="C4">
-        <v>258.1940065725964</v>
+        <v>255.8384489421479</v>
       </c>
       <c r="D4">
-        <v>247.1060065725964</v>
+        <v>246.9564489421479</v>
       </c>
       <c r="E4">
-        <v>-46.388</v>
+        <v>-44.182</v>
       </c>
       <c r="F4">
-        <v>4.412000000000001</v>
+        <v>6.618</v>
       </c>
       <c r="G4">
         <v>15.5</v>
@@ -1615,28 +1615,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M4">
-        <v>0.2219236</v>
+        <v>0.3328854</v>
       </c>
       <c r="N4">
-        <v>20.45358660408164</v>
+        <v>20.34262480408164</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>20.45358660408164</v>
+        <v>20.34262480408164</v>
       </c>
       <c r="Q4">
-        <v>28.55358660408163</v>
+        <v>28.44262480408164</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1147274434345846</v>
+        <v>0.1154380356349411</v>
       </c>
       <c r="T4">
-        <v>0.5904175733042778</v>
+        <v>0.5965043524105074</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>93.16499103331792</v>
+        <v>62.10999402221196</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1134838945658929</v>
+        <v>0.1135288945658929</v>
       </c>
       <c r="C5">
-        <v>255.8384489421479</v>
+        <v>253.4830722377375</v>
       </c>
       <c r="D5">
-        <v>246.9564489421479</v>
+        <v>246.8070722377375</v>
       </c>
       <c r="E5">
-        <v>-44.182</v>
+        <v>-41.976</v>
       </c>
       <c r="F5">
-        <v>6.618</v>
+        <v>8.824000000000002</v>
       </c>
       <c r="G5">
         <v>15.5</v>
@@ -1697,28 +1697,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M5">
-        <v>0.3328854</v>
+        <v>0.4438472000000001</v>
       </c>
       <c r="N5">
-        <v>20.34262480408164</v>
+        <v>20.23166300408164</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>20.34262480408164</v>
+        <v>20.23166300408164</v>
       </c>
       <c r="Q5">
-        <v>28.44262480408164</v>
+        <v>28.33166300408163</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1154380356349411</v>
+        <v>0.1161634318394718</v>
       </c>
       <c r="T5">
-        <v>0.5965043524105074</v>
+        <v>0.6027179394147836</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>62.10999402221196</v>
+        <v>46.58249551665896</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1135288945658929</v>
+        <v>0.1135738945658929</v>
       </c>
       <c r="C6">
-        <v>253.4830722377375</v>
+        <v>251.1278761312533</v>
       </c>
       <c r="D6">
-        <v>246.8070722377375</v>
+        <v>246.6578761312533</v>
       </c>
       <c r="E6">
-        <v>-41.976</v>
+        <v>-39.77</v>
       </c>
       <c r="F6">
-        <v>8.824000000000002</v>
+        <v>11.03</v>
       </c>
       <c r="G6">
         <v>15.5</v>
@@ -1779,28 +1779,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M6">
-        <v>0.4438472000000001</v>
+        <v>0.554809</v>
       </c>
       <c r="N6">
-        <v>20.23166300408164</v>
+        <v>20.12070120408164</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>20.23166300408164</v>
+        <v>20.12070120408164</v>
       </c>
       <c r="Q6">
-        <v>28.33166300408163</v>
+        <v>28.22070120408164</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1161634318394718</v>
+        <v>0.1169040995430451</v>
       </c>
       <c r="T6">
-        <v>0.6027179394147836</v>
+        <v>0.6090623387770444</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>46.58249551665896</v>
+        <v>37.26599641332718</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1135738945658929</v>
+        <v>0.1136188945658929</v>
       </c>
       <c r="C7">
-        <v>251.1278761312533</v>
+        <v>248.772860295376</v>
       </c>
       <c r="D7">
-        <v>246.6578761312533</v>
+        <v>246.508860295376</v>
       </c>
       <c r="E7">
-        <v>-39.77</v>
+        <v>-37.56399999999999</v>
       </c>
       <c r="F7">
-        <v>11.03</v>
+        <v>13.236</v>
       </c>
       <c r="G7">
         <v>15.5</v>
@@ -1861,28 +1861,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M7">
-        <v>0.554809</v>
+        <v>0.6657708000000001</v>
       </c>
       <c r="N7">
-        <v>20.12070120408164</v>
+        <v>20.00973940408164</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>20.12070120408164</v>
+        <v>20.00973940408164</v>
       </c>
       <c r="Q7">
-        <v>28.22070120408164</v>
+        <v>28.10973940408163</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1169040995430451</v>
+        <v>0.1176605261339286</v>
       </c>
       <c r="T7">
-        <v>0.6090623387770444</v>
+        <v>0.6155417253597789</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>37.26599641332718</v>
+        <v>31.05499701110597</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1136188945658929</v>
+        <v>0.1136638945658929</v>
       </c>
       <c r="C8">
-        <v>248.772860295376</v>
+        <v>246.418024403577</v>
       </c>
       <c r="D8">
-        <v>246.508860295376</v>
+        <v>246.360024403577</v>
       </c>
       <c r="E8">
-        <v>-37.56399999999999</v>
+        <v>-35.358</v>
       </c>
       <c r="F8">
-        <v>13.236</v>
+        <v>15.442</v>
       </c>
       <c r="G8">
         <v>15.5</v>
@@ -1943,28 +1943,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M8">
-        <v>0.6657708</v>
+        <v>0.7767326</v>
       </c>
       <c r="N8">
-        <v>20.00973940408164</v>
+        <v>19.89877760408164</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8">
-        <v>20.00973940408164</v>
+        <v>19.89877760408164</v>
       </c>
       <c r="Q8">
-        <v>28.10973940408163</v>
+        <v>27.99877760408163</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1176605261339286</v>
+        <v>0.1184332199633257</v>
       </c>
       <c r="T8">
-        <v>0.6155417253597789</v>
+        <v>0.6221604535894539</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>31.05499701110598</v>
+        <v>26.61856886666227</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1136638945658929</v>
+        <v>0.1137088945658929</v>
       </c>
       <c r="C9">
-        <v>246.418024403577</v>
+        <v>244.0633681301156</v>
       </c>
       <c r="D9">
-        <v>246.360024403577</v>
+        <v>246.2113681301156</v>
       </c>
       <c r="E9">
-        <v>-35.35799999999999</v>
+        <v>-33.15199999999999</v>
       </c>
       <c r="F9">
-        <v>15.442</v>
+        <v>17.648</v>
       </c>
       <c r="G9">
         <v>15.5</v>
@@ -2025,28 +2025,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M9">
-        <v>0.7767326000000001</v>
+        <v>0.8876944000000001</v>
       </c>
       <c r="N9">
-        <v>19.89877760408164</v>
+        <v>19.78781580408164</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9">
-        <v>19.89877760408164</v>
+        <v>19.78781580408164</v>
       </c>
       <c r="Q9">
-        <v>27.99877760408163</v>
+        <v>27.88781580408163</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1184332199633257</v>
+        <v>0.1192227114846662</v>
       </c>
       <c r="T9">
-        <v>0.6221604535894539</v>
+        <v>0.6289230672154262</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>26.61856886666227</v>
+        <v>23.29124775832948</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1137088945658929</v>
+        <v>0.1137538945658929</v>
       </c>
       <c r="C10">
-        <v>244.0633681301156</v>
+        <v>241.7088911500372</v>
       </c>
       <c r="D10">
-        <v>246.2113681301156</v>
+        <v>246.0628911500372</v>
       </c>
       <c r="E10">
-        <v>-33.15199999999999</v>
+        <v>-30.94599999999999</v>
       </c>
       <c r="F10">
-        <v>17.648</v>
+        <v>19.854</v>
       </c>
       <c r="G10">
         <v>15.5</v>
@@ -2107,28 +2107,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M10">
-        <v>0.8876944000000001</v>
+        <v>0.9986562000000001</v>
       </c>
       <c r="N10">
-        <v>19.78781580408164</v>
+        <v>19.67685400408164</v>
       </c>
       <c r="O10">
         <v>0</v>
       </c>
       <c r="P10">
-        <v>19.78781580408164</v>
+        <v>19.67685400408164</v>
       </c>
       <c r="Q10">
-        <v>27.88781580408163</v>
+        <v>27.77685400408163</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1192227114846662</v>
+        <v>0.1200295544680142</v>
       </c>
       <c r="T10">
-        <v>0.6289230672154262</v>
+        <v>0.6358343097122992</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>23.29124775832948</v>
+        <v>20.70333134073732</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1137538945658929</v>
+        <v>0.1137988945658929</v>
       </c>
       <c r="C11">
-        <v>241.7088911500372</v>
+        <v>239.3545931391703</v>
       </c>
       <c r="D11">
-        <v>246.0628911500372</v>
+        <v>245.9145931391703</v>
       </c>
       <c r="E11">
-        <v>-30.94599999999999</v>
+        <v>-28.74</v>
       </c>
       <c r="F11">
-        <v>19.854</v>
+        <v>22.06</v>
       </c>
       <c r="G11">
         <v>15.5</v>
@@ -2189,28 +2189,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M11">
-        <v>0.9986562000000001</v>
+        <v>1.109618</v>
       </c>
       <c r="N11">
-        <v>19.67685400408164</v>
+        <v>19.56589220408163</v>
       </c>
       <c r="O11">
         <v>0</v>
       </c>
       <c r="P11">
-        <v>19.67685400408164</v>
+        <v>19.56589220408163</v>
       </c>
       <c r="Q11">
-        <v>27.77685400408163</v>
+        <v>27.66589220408163</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1200295544680142</v>
+        <v>0.1208543272954365</v>
       </c>
       <c r="T11">
-        <v>0.6358343097122992</v>
+        <v>0.6428991353757691</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>20.70333134073732</v>
+        <v>18.63299820666359</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1137988945658929</v>
+        <v>0.1138438945658929</v>
       </c>
       <c r="C12">
-        <v>239.3545931391703</v>
+        <v>237.0004737741245</v>
       </c>
       <c r="D12">
-        <v>245.9145931391703</v>
+        <v>245.7664737741245</v>
       </c>
       <c r="E12">
-        <v>-28.73999999999999</v>
+        <v>-26.534</v>
       </c>
       <c r="F12">
-        <v>22.06</v>
+        <v>24.266</v>
       </c>
       <c r="G12">
         <v>15.5</v>
@@ -2271,28 +2271,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M12">
-        <v>1.109618</v>
+        <v>1.2205798</v>
       </c>
       <c r="N12">
-        <v>19.56589220408163</v>
+        <v>19.45493040408164</v>
       </c>
       <c r="O12">
         <v>0</v>
       </c>
       <c r="P12">
-        <v>19.56589220408163</v>
+        <v>19.45493040408164</v>
       </c>
       <c r="Q12">
-        <v>27.66589220408163</v>
+        <v>27.55493040408163</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1208543272954365</v>
+        <v>0.1216976343436999</v>
       </c>
       <c r="T12">
-        <v>0.6428991353757691</v>
+        <v>0.6501227211665082</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>18.63299820666359</v>
+        <v>16.93908927878508</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1138438945658929</v>
+        <v>0.1138888945658929</v>
       </c>
       <c r="C13">
-        <v>237.0004737741245</v>
+        <v>234.6465327322883</v>
       </c>
       <c r="D13">
-        <v>245.7664737741245</v>
+        <v>245.6185327322882</v>
       </c>
       <c r="E13">
-        <v>-26.534</v>
+        <v>-24.328</v>
       </c>
       <c r="F13">
-        <v>24.266</v>
+        <v>26.472</v>
       </c>
       <c r="G13">
         <v>15.5</v>
@@ -2353,28 +2353,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M13">
-        <v>1.2205798</v>
+        <v>1.3315416</v>
       </c>
       <c r="N13">
-        <v>19.45493040408164</v>
+        <v>19.34396860408163</v>
       </c>
       <c r="O13">
         <v>0</v>
       </c>
       <c r="P13">
-        <v>19.45493040408164</v>
+        <v>19.34396860408163</v>
       </c>
       <c r="Q13">
-        <v>27.55493040408163</v>
+        <v>27.44396860408163</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1216976343436999</v>
+        <v>0.1225601074612419</v>
       </c>
       <c r="T13">
-        <v>0.6501227211665082</v>
+        <v>0.6575104793615819</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>16.93908927878508</v>
+        <v>15.52749850555299</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1138888945658929</v>
+        <v>0.1139338945658929</v>
       </c>
       <c r="C14">
-        <v>234.6465327322883</v>
+        <v>232.2927696918257</v>
       </c>
       <c r="D14">
-        <v>245.6185327322882</v>
+        <v>245.4707696918257</v>
       </c>
       <c r="E14">
-        <v>-24.328</v>
+        <v>-22.12199999999999</v>
       </c>
       <c r="F14">
-        <v>26.472</v>
+        <v>28.678</v>
       </c>
       <c r="G14">
         <v>15.5</v>
@@ -2435,28 +2435,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M14">
-        <v>1.3315416</v>
+        <v>1.4425034</v>
       </c>
       <c r="N14">
-        <v>19.34396860408163</v>
+        <v>19.23300680408164</v>
       </c>
       <c r="O14">
         <v>0</v>
       </c>
       <c r="P14">
-        <v>19.34396860408163</v>
+        <v>19.23300680408164</v>
       </c>
       <c r="Q14">
-        <v>27.44396860408163</v>
+        <v>27.33300680408163</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1225601074612419</v>
+        <v>0.1234424075470033</v>
       </c>
       <c r="T14">
-        <v>0.6575104793615819</v>
+        <v>0.6650680710783818</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>15.52749850555299</v>
+        <v>14.33307554358737</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1139338945658929</v>
+        <v>0.1139788945658929</v>
       </c>
       <c r="C15">
-        <v>232.2927696918257</v>
+        <v>229.9391843316759</v>
       </c>
       <c r="D15">
-        <v>245.4707696918257</v>
+        <v>245.3231843316759</v>
       </c>
       <c r="E15">
-        <v>-22.12199999999999</v>
+        <v>-19.91599999999999</v>
       </c>
       <c r="F15">
-        <v>28.678</v>
+        <v>30.88400000000001</v>
       </c>
       <c r="G15">
         <v>15.5</v>
@@ -2517,28 +2517,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M15">
-        <v>1.4425034</v>
+        <v>1.5534652</v>
       </c>
       <c r="N15">
-        <v>19.23300680408164</v>
+        <v>19.12204500408163</v>
       </c>
       <c r="O15">
         <v>0</v>
       </c>
       <c r="P15">
-        <v>19.23300680408164</v>
+        <v>19.12204500408163</v>
       </c>
       <c r="Q15">
-        <v>27.33300680408163</v>
+        <v>27.22204500408163</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1234424075470033</v>
+        <v>0.1243452262394103</v>
       </c>
       <c r="T15">
-        <v>0.6650680710783818</v>
+        <v>0.6728014207420839</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>14.33307554358737</v>
+        <v>13.30928443333113</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1139788945658929</v>
+        <v>0.1142488945658929</v>
       </c>
       <c r="C16">
-        <v>229.9391843316759</v>
+        <v>226.8513855748411</v>
       </c>
       <c r="D16">
-        <v>245.3231843316759</v>
+        <v>244.4413855748411</v>
       </c>
       <c r="E16">
-        <v>-19.91599999999999</v>
+        <v>-17.70999999999999</v>
       </c>
       <c r="F16">
-        <v>30.88400000000001</v>
+        <v>33.09000000000001</v>
       </c>
       <c r="G16">
         <v>15.5</v>
@@ -2599,45 +2599,45 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M16">
-        <v>1.5534652</v>
+        <v>1.714062</v>
       </c>
       <c r="N16">
-        <v>19.12204500408163</v>
+        <v>18.96144820408163</v>
       </c>
       <c r="O16">
         <v>0</v>
       </c>
       <c r="P16">
-        <v>19.12204500408163</v>
+        <v>18.96144820408163</v>
       </c>
       <c r="Q16">
-        <v>27.22204500408163</v>
+        <v>27.06144820408163</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1243452262394103</v>
+        <v>0.1252692877245799</v>
       </c>
       <c r="T16">
-        <v>0.6728014207420839</v>
+        <v>0.6807167315743438</v>
       </c>
       <c r="U16">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V16">
         <v>0</v>
       </c>
       <c r="W16">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y16">
-        <v>13.30928443333113</v>
+        <v>12.06228841435236</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1142488945658929</v>
+        <v>0.1143088945658929</v>
       </c>
       <c r="C17">
-        <v>226.8513855748411</v>
+        <v>224.4502904793718</v>
       </c>
       <c r="D17">
-        <v>244.4413855748411</v>
+        <v>244.2462904793718</v>
       </c>
       <c r="E17">
-        <v>-17.70999999999999</v>
+        <v>-15.50399999999999</v>
       </c>
       <c r="F17">
-        <v>33.09</v>
+        <v>35.29600000000001</v>
       </c>
       <c r="G17">
         <v>15.5</v>
@@ -2681,28 +2681,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M17">
-        <v>1.714062</v>
+        <v>1.8283328</v>
       </c>
       <c r="N17">
-        <v>18.96144820408163</v>
+        <v>18.84717740408163</v>
       </c>
       <c r="O17">
         <v>0</v>
       </c>
       <c r="P17">
-        <v>18.96144820408163</v>
+        <v>18.84717740408163</v>
       </c>
       <c r="Q17">
-        <v>27.06144820408163</v>
+        <v>26.94717740408163</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1252692877245799</v>
+        <v>0.126215350673682</v>
       </c>
       <c r="T17">
-        <v>0.6807167315743438</v>
+        <v>0.688820502188324</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>12.06228841435236</v>
+        <v>11.30839538845533</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1143088945658929</v>
+        <v>0.1143688945658929</v>
       </c>
       <c r="C18">
-        <v>224.4502904793718</v>
+        <v>222.0495065565956</v>
       </c>
       <c r="D18">
-        <v>244.2462904793718</v>
+        <v>244.0515065565957</v>
       </c>
       <c r="E18">
-        <v>-15.50399999999999</v>
+        <v>-13.29799999999999</v>
       </c>
       <c r="F18">
-        <v>35.29600000000001</v>
+        <v>37.50200000000001</v>
       </c>
       <c r="G18">
         <v>15.5</v>
@@ -2763,28 +2763,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M18">
-        <v>1.8283328</v>
+        <v>1.9426036</v>
       </c>
       <c r="N18">
-        <v>18.84717740408163</v>
+        <v>18.73290660408163</v>
       </c>
       <c r="O18">
         <v>0</v>
       </c>
       <c r="P18">
-        <v>18.84717740408163</v>
+        <v>18.73290660408163</v>
       </c>
       <c r="Q18">
-        <v>26.94717740408163</v>
+        <v>26.83290660408163</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.126215350673682</v>
+        <v>0.1271842103203529</v>
       </c>
       <c r="T18">
-        <v>0.688820502188324</v>
+        <v>0.6971195443833641</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.30839538845533</v>
+        <v>10.64319565972267</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1143688945658929</v>
+        <v>0.1144288945658929</v>
       </c>
       <c r="C19">
-        <v>222.0495065565956</v>
+        <v>219.6490330626347</v>
       </c>
       <c r="D19">
-        <v>244.0515065565957</v>
+        <v>243.8570330626348</v>
       </c>
       <c r="E19">
-        <v>-13.29799999999999</v>
+        <v>-11.09199999999999</v>
       </c>
       <c r="F19">
-        <v>37.50200000000001</v>
+        <v>39.70800000000001</v>
       </c>
       <c r="G19">
         <v>15.5</v>
@@ -2845,28 +2845,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M19">
-        <v>1.9426036</v>
+        <v>2.0568744</v>
       </c>
       <c r="N19">
-        <v>18.73290660408163</v>
+        <v>18.61863580408163</v>
       </c>
       <c r="O19">
         <v>0</v>
       </c>
       <c r="P19">
-        <v>18.73290660408163</v>
+        <v>18.61863580408163</v>
       </c>
       <c r="Q19">
-        <v>26.83290660408163</v>
+        <v>26.71863580408163</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1271842103203529</v>
+        <v>0.1281767006901133</v>
       </c>
       <c r="T19">
-        <v>0.6971195443833641</v>
+        <v>0.7056210022416978</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>10.64319565972267</v>
+        <v>10.0519070119603</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1144288945658929</v>
+        <v>0.1148118945658929</v>
       </c>
       <c r="C20">
-        <v>219.6490330626347</v>
+        <v>216.2089106032965</v>
       </c>
       <c r="D20">
-        <v>243.8570330626347</v>
+        <v>242.6229106032965</v>
       </c>
       <c r="E20">
-        <v>-11.09199999999999</v>
+        <v>-8.885999999999996</v>
       </c>
       <c r="F20">
-        <v>39.70800000000001</v>
+        <v>41.914</v>
       </c>
       <c r="G20">
         <v>15.5</v>
@@ -2927,45 +2927,45 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M20">
-        <v>2.0568744</v>
+        <v>2.242399</v>
       </c>
       <c r="N20">
-        <v>18.61863580408163</v>
+        <v>18.43311120408164</v>
       </c>
       <c r="O20">
         <v>0</v>
       </c>
       <c r="P20">
-        <v>18.61863580408163</v>
+        <v>18.43311120408164</v>
       </c>
       <c r="Q20">
-        <v>26.71863580408163</v>
+        <v>26.53311120408164</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1281767006901133</v>
+        <v>0.1291936969949295</v>
       </c>
       <c r="T20">
-        <v>0.7056210022416978</v>
+        <v>0.7143323726397434</v>
       </c>
       <c r="U20">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V20">
         <v>0</v>
       </c>
       <c r="W20">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>10.0519070119603</v>
+        <v>9.220263746140466</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1148118945658929</v>
+        <v>0.1148888945658929</v>
       </c>
       <c r="C21">
-        <v>216.2089106032965</v>
+        <v>213.7563037850933</v>
       </c>
       <c r="D21">
-        <v>242.6229106032965</v>
+        <v>242.3763037850933</v>
       </c>
       <c r="E21">
-        <v>-8.885999999999996</v>
+        <v>-6.679999999999993</v>
       </c>
       <c r="F21">
-        <v>41.914</v>
+        <v>44.12</v>
       </c>
       <c r="G21">
         <v>15.5</v>
@@ -3009,28 +3009,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M21">
-        <v>2.242399</v>
+        <v>2.36042</v>
       </c>
       <c r="N21">
-        <v>18.43311120408164</v>
+        <v>18.31509020408163</v>
       </c>
       <c r="O21">
         <v>0</v>
       </c>
       <c r="P21">
-        <v>18.43311120408164</v>
+        <v>18.31509020408163</v>
       </c>
       <c r="Q21">
-        <v>26.53311120408164</v>
+        <v>26.41509020408163</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1291936969949295</v>
+        <v>0.1302361182073661</v>
       </c>
       <c r="T21">
-        <v>0.7143323726397434</v>
+        <v>0.7232615272977403</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>9.220263746140466</v>
+        <v>8.759250558833442</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1148888945658929</v>
+        <v>0.1149658945658929</v>
       </c>
       <c r="C22">
-        <v>213.7563037850933</v>
+        <v>211.3041977701482</v>
       </c>
       <c r="D22">
-        <v>242.3763037850933</v>
+        <v>242.1301977701482</v>
       </c>
       <c r="E22">
-        <v>-6.679999999999993</v>
+        <v>-4.47399999999999</v>
       </c>
       <c r="F22">
-        <v>44.12</v>
+        <v>46.32600000000001</v>
       </c>
       <c r="G22">
         <v>15.5</v>
@@ -3091,28 +3091,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M22">
-        <v>2.36042</v>
+        <v>2.478441000000001</v>
       </c>
       <c r="N22">
-        <v>18.31509020408163</v>
+        <v>18.19706920408164</v>
       </c>
       <c r="O22">
         <v>0</v>
       </c>
       <c r="P22">
-        <v>18.31509020408163</v>
+        <v>18.19706920408164</v>
       </c>
       <c r="Q22">
-        <v>26.41509020408163</v>
+        <v>26.29706920408163</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1302361182073661</v>
+        <v>0.1313049298302442</v>
       </c>
       <c r="T22">
-        <v>0.7232615272977403</v>
+        <v>0.7324167365040408</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.759250558833442</v>
+        <v>8.342143389365182</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1149658945658929</v>
+        <v>0.1150428945658929</v>
       </c>
       <c r="C23">
-        <v>211.3041977701482</v>
+        <v>208.8525910344793</v>
       </c>
       <c r="D23">
-        <v>242.1301977701482</v>
+        <v>241.8845910344793</v>
       </c>
       <c r="E23">
-        <v>-4.473999999999997</v>
+        <v>-2.267999999999994</v>
       </c>
       <c r="F23">
-        <v>46.326</v>
+        <v>48.532</v>
       </c>
       <c r="G23">
         <v>15.5</v>
@@ -3173,28 +3173,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M23">
-        <v>2.478441</v>
+        <v>2.596462</v>
       </c>
       <c r="N23">
-        <v>18.19706920408164</v>
+        <v>18.07904820408164</v>
       </c>
       <c r="O23">
         <v>0</v>
       </c>
       <c r="P23">
-        <v>18.19706920408164</v>
+        <v>18.07904820408164</v>
       </c>
       <c r="Q23">
-        <v>26.29706920408163</v>
+        <v>26.17904820408164</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1313049298302442</v>
+        <v>0.1324011468793498</v>
       </c>
       <c r="T23">
-        <v>0.7324167365040408</v>
+        <v>0.7418066946643489</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.342143389365184</v>
+        <v>7.962955053484948</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1150428945658929</v>
+        <v>0.1151198945658929</v>
       </c>
       <c r="C24">
-        <v>208.8525910344793</v>
+        <v>206.4014820602824</v>
       </c>
       <c r="D24">
-        <v>241.8845910344793</v>
+        <v>241.6394820602824</v>
       </c>
       <c r="E24">
-        <v>-2.267999999999994</v>
+        <v>-0.06199999999999051</v>
       </c>
       <c r="F24">
-        <v>48.532</v>
+        <v>50.73800000000001</v>
       </c>
       <c r="G24">
         <v>15.5</v>
@@ -3255,28 +3255,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M24">
-        <v>2.596462</v>
+        <v>2.714483</v>
       </c>
       <c r="N24">
-        <v>18.07904820408164</v>
+        <v>17.96102720408163</v>
       </c>
       <c r="O24">
         <v>0</v>
       </c>
       <c r="P24">
-        <v>18.07904820408164</v>
+        <v>17.96102720408163</v>
       </c>
       <c r="Q24">
-        <v>26.17904820408164</v>
+        <v>26.06102720408163</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1324011468793498</v>
+        <v>0.1335258370985622</v>
       </c>
       <c r="T24">
-        <v>0.7418066946643489</v>
+        <v>0.751440547841808</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>7.962955053484948</v>
+        <v>7.616739616376906</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1151198945658929</v>
+        <v>0.1153888945658929</v>
       </c>
       <c r="C25">
-        <v>206.4014820602824</v>
+        <v>203.3430775482679</v>
       </c>
       <c r="D25">
-        <v>241.6394820602824</v>
+        <v>240.7870775482679</v>
       </c>
       <c r="E25">
-        <v>-0.06199999999999051</v>
+        <v>2.144000000000013</v>
       </c>
       <c r="F25">
-        <v>50.73800000000001</v>
+        <v>52.94400000000001</v>
       </c>
       <c r="G25">
         <v>15.5</v>
@@ -3337,45 +3337,45 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M25">
-        <v>2.714483</v>
+        <v>2.8748592</v>
       </c>
       <c r="N25">
-        <v>17.96102720408163</v>
+        <v>17.80065100408164</v>
       </c>
       <c r="O25">
         <v>0</v>
       </c>
       <c r="P25">
-        <v>17.96102720408163</v>
+        <v>17.80065100408164</v>
       </c>
       <c r="Q25">
-        <v>26.06102720408163</v>
+        <v>25.90065100408163</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1335258370985622</v>
+        <v>0.1346801244288064</v>
       </c>
       <c r="T25">
-        <v>0.751440547841808</v>
+        <v>0.7613279234713055</v>
       </c>
       <c r="U25">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V25">
         <v>0</v>
       </c>
       <c r="W25">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y25">
-        <v>7.616739616376906</v>
+        <v>7.191834022369386</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1153888945658929</v>
+        <v>0.1154738945658929</v>
       </c>
       <c r="C26">
-        <v>203.3430775482679</v>
+        <v>200.8689793831068</v>
       </c>
       <c r="D26">
-        <v>240.7870775482679</v>
+        <v>240.5189793831068</v>
       </c>
       <c r="E26">
-        <v>2.144000000000005</v>
+        <v>4.350000000000009</v>
       </c>
       <c r="F26">
-        <v>52.944</v>
+        <v>55.15000000000001</v>
       </c>
       <c r="G26">
         <v>15.5</v>
@@ -3419,28 +3419,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M26">
-        <v>2.8748592</v>
+        <v>2.994645</v>
       </c>
       <c r="N26">
-        <v>17.80065100408164</v>
+        <v>17.68086520408163</v>
       </c>
       <c r="O26">
         <v>0</v>
       </c>
       <c r="P26">
-        <v>17.80065100408164</v>
+        <v>17.68086520408163</v>
       </c>
       <c r="Q26">
-        <v>25.90065100408163</v>
+        <v>25.78086520408163</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1346801244288064</v>
+        <v>0.1358651927545239</v>
       </c>
       <c r="T26">
-        <v>0.7613279234713055</v>
+        <v>0.7714789624509228</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.191834022369386</v>
+        <v>6.904160661474609</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1154738945658929</v>
+        <v>0.1155588945658929</v>
       </c>
       <c r="C27">
-        <v>200.8689793831068</v>
+        <v>198.3954775679386</v>
       </c>
       <c r="D27">
-        <v>240.5189793831068</v>
+        <v>240.2514775679386</v>
       </c>
       <c r="E27">
-        <v>4.350000000000009</v>
+        <v>6.556000000000012</v>
       </c>
       <c r="F27">
-        <v>55.15000000000001</v>
+        <v>57.35600000000001</v>
       </c>
       <c r="G27">
         <v>15.5</v>
@@ -3501,28 +3501,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M27">
-        <v>2.994645</v>
+        <v>3.1144308</v>
       </c>
       <c r="N27">
-        <v>17.68086520408163</v>
+        <v>17.56107940408164</v>
       </c>
       <c r="O27">
         <v>0</v>
       </c>
       <c r="P27">
-        <v>17.68086520408163</v>
+        <v>17.56107940408164</v>
       </c>
       <c r="Q27">
-        <v>25.78086520408163</v>
+        <v>25.66107940408163</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1358651927545239</v>
+        <v>0.1370822899539093</v>
       </c>
       <c r="T27">
-        <v>0.7714789624509228</v>
+        <v>0.7819043538353948</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>6.904160661474609</v>
+        <v>6.638616020648663</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1155588945658929</v>
+        <v>0.1156438945658929</v>
       </c>
       <c r="C28">
-        <v>198.3954775679386</v>
+        <v>195.9225701152177</v>
       </c>
       <c r="D28">
-        <v>240.2514775679386</v>
+        <v>239.9845701152177</v>
       </c>
       <c r="E28">
-        <v>6.556000000000012</v>
+        <v>8.762000000000015</v>
       </c>
       <c r="F28">
-        <v>57.35600000000001</v>
+        <v>59.56200000000001</v>
       </c>
       <c r="G28">
         <v>15.5</v>
@@ -3583,28 +3583,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M28">
-        <v>3.1144308</v>
+        <v>3.234216600000001</v>
       </c>
       <c r="N28">
-        <v>17.56107940408164</v>
+        <v>17.44129360408164</v>
       </c>
       <c r="O28">
         <v>0</v>
       </c>
       <c r="P28">
-        <v>17.56107940408164</v>
+        <v>17.44129360408164</v>
       </c>
       <c r="Q28">
-        <v>25.66107940408163</v>
+        <v>25.54129360408163</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1370822899539093</v>
+        <v>0.1383327322820451</v>
       </c>
       <c r="T28">
-        <v>0.7819043538353948</v>
+        <v>0.7926153723810853</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.638616020648663</v>
+        <v>6.392741353217231</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1156438945658929</v>
+        <v>0.1157288945658929</v>
       </c>
       <c r="C29">
-        <v>195.9225701152177</v>
+        <v>193.4502550462208</v>
       </c>
       <c r="D29">
-        <v>239.9845701152177</v>
+        <v>239.7182550462208</v>
       </c>
       <c r="E29">
-        <v>8.762000000000015</v>
+        <v>10.96800000000002</v>
       </c>
       <c r="F29">
-        <v>59.56200000000001</v>
+        <v>61.76800000000001</v>
       </c>
       <c r="G29">
         <v>15.5</v>
@@ -3665,28 +3665,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M29">
-        <v>3.234216600000001</v>
+        <v>3.354002400000001</v>
       </c>
       <c r="N29">
-        <v>17.44129360408164</v>
+        <v>17.32150780408163</v>
       </c>
       <c r="O29">
         <v>0</v>
       </c>
       <c r="P29">
-        <v>17.44129360408164</v>
+        <v>17.32150780408163</v>
       </c>
       <c r="Q29">
-        <v>25.54129360408163</v>
+        <v>25.42150780408163</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1383327322820451</v>
+        <v>0.1396179091192957</v>
       </c>
       <c r="T29">
-        <v>0.7926153723810853</v>
+        <v>0.8036239192197113</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.392741353217231</v>
+        <v>6.1644291620309</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1157288945658929</v>
+        <v>0.1161038945658929</v>
       </c>
       <c r="C30">
-        <v>193.4502550462208</v>
+        <v>190.0763572611785</v>
       </c>
       <c r="D30">
-        <v>239.7182550462208</v>
+        <v>238.5503572611785</v>
       </c>
       <c r="E30">
-        <v>10.96800000000002</v>
+        <v>13.17400000000002</v>
       </c>
       <c r="F30">
-        <v>61.76800000000001</v>
+        <v>63.97400000000002</v>
       </c>
       <c r="G30">
         <v>15.5</v>
@@ -3747,45 +3747,45 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M30">
-        <v>3.354002400000001</v>
+        <v>3.537762200000001</v>
       </c>
       <c r="N30">
-        <v>17.32150780408163</v>
+        <v>17.13774800408164</v>
       </c>
       <c r="O30">
         <v>0</v>
       </c>
       <c r="P30">
-        <v>17.32150780408163</v>
+        <v>17.13774800408164</v>
       </c>
       <c r="Q30">
-        <v>25.42150780408163</v>
+        <v>25.23774800408163</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1396179091192957</v>
+        <v>0.1409392881209759</v>
       </c>
       <c r="T30">
-        <v>0.8036239192197113</v>
+        <v>0.8149425659692848</v>
       </c>
       <c r="U30">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V30">
         <v>0</v>
       </c>
       <c r="W30">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y30">
-        <v>6.1644291620309</v>
+        <v>5.844234020048502</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1161038945658929</v>
+        <v>0.1161988945658929</v>
       </c>
       <c r="C31">
-        <v>190.0763572611785</v>
+        <v>187.5762942180735</v>
       </c>
       <c r="D31">
-        <v>238.5503572611786</v>
+        <v>238.2562942180735</v>
       </c>
       <c r="E31">
-        <v>13.17400000000001</v>
+        <v>15.38000000000001</v>
       </c>
       <c r="F31">
-        <v>63.974</v>
+        <v>66.18000000000001</v>
       </c>
       <c r="G31">
         <v>15.5</v>
@@ -3829,28 +3829,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M31">
-        <v>3.5377622</v>
+        <v>3.659754</v>
       </c>
       <c r="N31">
-        <v>17.13774800408164</v>
+        <v>17.01575620408164</v>
       </c>
       <c r="O31">
         <v>0</v>
       </c>
       <c r="P31">
-        <v>17.13774800408164</v>
+        <v>17.01575620408164</v>
       </c>
       <c r="Q31">
-        <v>25.23774800408163</v>
+        <v>25.11575620408163</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1409392881209759</v>
+        <v>0.1422984208084184</v>
       </c>
       <c r="T31">
-        <v>0.8149425659692847</v>
+        <v>0.8265846026259889</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.844234020048503</v>
+        <v>5.649426219380219</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1161988945658929</v>
+        <v>0.1162938945658929</v>
       </c>
       <c r="C32">
-        <v>187.5762942180735</v>
+        <v>185.0769552703709</v>
       </c>
       <c r="D32">
-        <v>238.2562942180735</v>
+        <v>237.9629552703709</v>
       </c>
       <c r="E32">
-        <v>15.38000000000001</v>
+        <v>17.58600000000001</v>
       </c>
       <c r="F32">
-        <v>66.18000000000001</v>
+        <v>68.38600000000001</v>
       </c>
       <c r="G32">
         <v>15.5</v>
@@ -3911,28 +3911,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M32">
-        <v>3.659754</v>
+        <v>3.781745800000001</v>
       </c>
       <c r="N32">
-        <v>17.01575620408164</v>
+        <v>16.89376440408164</v>
       </c>
       <c r="O32">
         <v>0</v>
       </c>
       <c r="P32">
-        <v>17.01575620408164</v>
+        <v>16.89376440408164</v>
       </c>
       <c r="Q32">
-        <v>25.11575620408163</v>
+        <v>24.99376440408163</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1422984208084184</v>
+        <v>0.1436969486462216</v>
       </c>
       <c r="T32">
-        <v>0.8265846026259889</v>
+        <v>0.8385640896205684</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.649426219380219</v>
+        <v>5.46718666391634</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1162938945658929</v>
+        <v>0.1163888945658929</v>
       </c>
       <c r="C33">
-        <v>185.0769552703709</v>
+        <v>182.5783377468608</v>
       </c>
       <c r="D33">
-        <v>237.9629552703709</v>
+        <v>237.6703377468608</v>
       </c>
       <c r="E33">
-        <v>17.58600000000001</v>
+        <v>19.79200000000002</v>
       </c>
       <c r="F33">
-        <v>68.38600000000001</v>
+        <v>70.59200000000001</v>
       </c>
       <c r="G33">
         <v>15.5</v>
@@ -3993,28 +3993,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M33">
-        <v>3.781745800000001</v>
+        <v>3.903737600000001</v>
       </c>
       <c r="N33">
-        <v>16.89376440408164</v>
+        <v>16.77177260408164</v>
       </c>
       <c r="O33">
         <v>0</v>
       </c>
       <c r="P33">
-        <v>16.89376440408164</v>
+        <v>16.77177260408164</v>
       </c>
       <c r="Q33">
-        <v>24.99376440408163</v>
+        <v>24.87177260408163</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1436969486462216</v>
+        <v>0.1451366096557249</v>
       </c>
       <c r="T33">
-        <v>0.8385640896205684</v>
+        <v>0.8508959144679298</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.46718666391634</v>
+        <v>5.296337080668955</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1163888945658929</v>
+        <v>0.1164838945658929</v>
       </c>
       <c r="C34">
-        <v>182.5783377468608</v>
+        <v>180.0804389894561</v>
       </c>
       <c r="D34">
-        <v>237.6703377468608</v>
+        <v>237.3784389894561</v>
       </c>
       <c r="E34">
-        <v>19.79200000000002</v>
+        <v>21.99800000000002</v>
       </c>
       <c r="F34">
-        <v>70.59200000000001</v>
+        <v>72.79800000000002</v>
       </c>
       <c r="G34">
         <v>15.5</v>
@@ -4075,28 +4075,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M34">
-        <v>3.903737600000001</v>
+        <v>4.025729400000001</v>
       </c>
       <c r="N34">
-        <v>16.77177260408164</v>
+        <v>16.64978080408164</v>
       </c>
       <c r="O34">
         <v>0</v>
       </c>
       <c r="P34">
-        <v>16.77177260408164</v>
+        <v>16.64978080408164</v>
       </c>
       <c r="Q34">
-        <v>24.87177260408163</v>
+        <v>24.74978080408163</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1451366096557249</v>
+        <v>0.1466192456207357</v>
       </c>
       <c r="T34">
-        <v>0.8508959144679298</v>
+        <v>0.8635958534898391</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.296337080668955</v>
+        <v>5.13584201761838</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1164838945658929</v>
+        <v>0.1165788945658929</v>
       </c>
       <c r="C35">
-        <v>180.0804389894561</v>
+        <v>177.5832563531118</v>
       </c>
       <c r="D35">
-        <v>237.3784389894561</v>
+        <v>237.0872563531118</v>
       </c>
       <c r="E35">
-        <v>21.99800000000002</v>
+        <v>24.20400000000002</v>
       </c>
       <c r="F35">
-        <v>72.79800000000002</v>
+        <v>75.00400000000002</v>
       </c>
       <c r="G35">
         <v>15.5</v>
@@ -4157,28 +4157,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M35">
-        <v>4.025729400000001</v>
+        <v>4.147721200000001</v>
       </c>
       <c r="N35">
-        <v>16.64978080408164</v>
+        <v>16.52778900408163</v>
       </c>
       <c r="O35">
         <v>0</v>
       </c>
       <c r="P35">
-        <v>16.64978080408164</v>
+        <v>16.52778900408163</v>
       </c>
       <c r="Q35">
-        <v>24.74978080408163</v>
+        <v>24.62778900408163</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1466192456207357</v>
+        <v>0.1481468099483225</v>
       </c>
       <c r="T35">
-        <v>0.8635958534898391</v>
+        <v>0.876680639148776</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.13584201761838</v>
+        <v>4.984787840629604</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1165788945658929</v>
+        <v>0.1166738945658929</v>
       </c>
       <c r="C36">
-        <v>177.5832563531118</v>
+        <v>175.0867872057453</v>
       </c>
       <c r="D36">
-        <v>237.0872563531118</v>
+        <v>236.7967872057454</v>
       </c>
       <c r="E36">
-        <v>24.20400000000002</v>
+        <v>26.41000000000003</v>
       </c>
       <c r="F36">
-        <v>75.00400000000002</v>
+        <v>77.21000000000002</v>
       </c>
       <c r="G36">
         <v>15.5</v>
@@ -4239,28 +4239,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M36">
-        <v>4.147721200000001</v>
+        <v>4.269713000000001</v>
       </c>
       <c r="N36">
-        <v>16.52778900408163</v>
+        <v>16.40579720408164</v>
       </c>
       <c r="O36">
         <v>0</v>
       </c>
       <c r="P36">
-        <v>16.52778900408163</v>
+        <v>16.40579720408164</v>
       </c>
       <c r="Q36">
-        <v>24.62778900408163</v>
+        <v>24.50579720408163</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1481468099483225</v>
+        <v>0.1497213762552198</v>
       </c>
       <c r="T36">
-        <v>0.876680639148776</v>
+        <v>0.8901680335972189</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.984787840629604</v>
+        <v>4.84236533089733</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1166738945658929</v>
+        <v>0.1167688945658929</v>
       </c>
       <c r="C37">
-        <v>175.0867872057453</v>
+        <v>172.5910289281575</v>
       </c>
       <c r="D37">
-        <v>236.7967872057454</v>
+        <v>236.5070289281575</v>
       </c>
       <c r="E37">
-        <v>26.41000000000003</v>
+        <v>28.61600000000001</v>
       </c>
       <c r="F37">
-        <v>77.21000000000002</v>
+        <v>79.41600000000001</v>
       </c>
       <c r="G37">
         <v>15.5</v>
@@ -4321,28 +4321,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M37">
-        <v>4.269713000000001</v>
+        <v>4.391704800000001</v>
       </c>
       <c r="N37">
-        <v>16.40579720408164</v>
+        <v>16.28380540408163</v>
       </c>
       <c r="O37">
         <v>0</v>
       </c>
       <c r="P37">
-        <v>16.40579720408164</v>
+        <v>16.28380540408163</v>
       </c>
       <c r="Q37">
-        <v>24.50579720408163</v>
+        <v>24.38380540408163</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1497213762552198</v>
+        <v>0.1513451477592077</v>
       </c>
       <c r="T37">
-        <v>0.8901680335972189</v>
+        <v>0.9040769091221753</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.84236533089733</v>
+        <v>4.707855182816848</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1167688945658929</v>
+        <v>0.1168638945658929</v>
       </c>
       <c r="C38">
-        <v>172.5910289281574</v>
+        <v>170.0959789139528</v>
       </c>
       <c r="D38">
-        <v>236.5070289281574</v>
+        <v>236.2179789139529</v>
       </c>
       <c r="E38">
-        <v>28.61600000000001</v>
+        <v>30.82200000000002</v>
       </c>
       <c r="F38">
-        <v>79.41600000000001</v>
+        <v>81.62200000000001</v>
       </c>
       <c r="G38">
         <v>15.5</v>
@@ -4403,28 +4403,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M38">
-        <v>4.391704800000001</v>
+        <v>4.513696600000001</v>
       </c>
       <c r="N38">
-        <v>16.28380540408163</v>
+        <v>16.16181360408164</v>
       </c>
       <c r="O38">
         <v>0</v>
       </c>
       <c r="P38">
-        <v>16.28380540408163</v>
+        <v>16.16181360408164</v>
       </c>
       <c r="Q38">
-        <v>24.38380540408163</v>
+        <v>24.26181360408163</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1513451477592077</v>
+        <v>0.1530204675649094</v>
       </c>
       <c r="T38">
-        <v>0.9040769091221753</v>
+        <v>0.9184273362510987</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.707855182816848</v>
+        <v>4.580615853551528</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1168638945658929</v>
+        <v>0.1179088945658929</v>
       </c>
       <c r="C39">
-        <v>170.0959789139528</v>
+        <v>164.7564412973126</v>
       </c>
       <c r="D39">
-        <v>236.2179789139529</v>
+        <v>233.0844412973126</v>
       </c>
       <c r="E39">
-        <v>30.82200000000002</v>
+        <v>33.02800000000001</v>
       </c>
       <c r="F39">
-        <v>81.62200000000001</v>
+        <v>83.828</v>
       </c>
       <c r="G39">
         <v>15.5</v>
@@ -4485,45 +4485,45 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M39">
-        <v>4.513696600000001</v>
+        <v>4.845258400000001</v>
       </c>
       <c r="N39">
-        <v>16.16181360408164</v>
+        <v>15.83025180408164</v>
       </c>
       <c r="O39">
         <v>0</v>
       </c>
       <c r="P39">
-        <v>16.16181360408164</v>
+        <v>15.83025180408164</v>
       </c>
       <c r="Q39">
-        <v>24.26181360408163</v>
+        <v>23.93025180408164</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1530204675649094</v>
+        <v>0.1547498299449885</v>
       </c>
       <c r="T39">
-        <v>0.9184273362510987</v>
+        <v>0.9332406803841808</v>
       </c>
       <c r="U39">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V39">
         <v>0</v>
       </c>
       <c r="W39">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y39">
-        <v>4.580615853551528</v>
+        <v>4.26716358493525</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1179088945658929</v>
+        <v>0.1180288945658929</v>
       </c>
       <c r="C40">
-        <v>164.7564412973126</v>
+        <v>162.195922600751</v>
       </c>
       <c r="D40">
-        <v>233.0844412973126</v>
+        <v>232.729922600751</v>
       </c>
       <c r="E40">
-        <v>33.02800000000001</v>
+        <v>35.23400000000001</v>
       </c>
       <c r="F40">
-        <v>83.828</v>
+        <v>86.03400000000001</v>
       </c>
       <c r="G40">
         <v>15.5</v>
@@ -4567,28 +4567,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M40">
-        <v>4.845258400000001</v>
+        <v>4.9727652</v>
       </c>
       <c r="N40">
-        <v>15.83025180408164</v>
+        <v>15.70274500408163</v>
       </c>
       <c r="O40">
         <v>0</v>
       </c>
       <c r="P40">
-        <v>15.83025180408164</v>
+        <v>15.70274500408163</v>
       </c>
       <c r="Q40">
-        <v>23.93025180408164</v>
+        <v>23.80274500408163</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1547498299449885</v>
+        <v>0.156535892730972</v>
       </c>
       <c r="T40">
-        <v>0.9332406803841808</v>
+        <v>0.9485397079314626</v>
       </c>
       <c r="U40">
         <v>0.0578</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.26716358493525</v>
+        <v>4.157749134039475</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1180288945658929</v>
+        <v>0.1181488945658929</v>
       </c>
       <c r="C41">
-        <v>162.195922600751</v>
+        <v>159.6364807039338</v>
       </c>
       <c r="D41">
-        <v>232.729922600751</v>
+        <v>232.3764807039338</v>
       </c>
       <c r="E41">
-        <v>35.23400000000001</v>
+        <v>37.44000000000001</v>
       </c>
       <c r="F41">
-        <v>86.03400000000001</v>
+        <v>88.24000000000001</v>
       </c>
       <c r="G41">
         <v>15.5</v>
@@ -4649,28 +4649,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M41">
-        <v>4.9727652</v>
+        <v>5.100272000000001</v>
       </c>
       <c r="N41">
-        <v>15.70274500408163</v>
+        <v>15.57523820408164</v>
       </c>
       <c r="O41">
         <v>0</v>
       </c>
       <c r="P41">
-        <v>15.70274500408163</v>
+        <v>15.57523820408164</v>
       </c>
       <c r="Q41">
-        <v>23.80274500408163</v>
+        <v>23.67523820408163</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.156535892730972</v>
+        <v>0.1583814909431548</v>
       </c>
       <c r="T41">
-        <v>0.9485397079314626</v>
+        <v>0.9643487030636537</v>
       </c>
       <c r="U41">
         <v>0.0578</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.157749134039475</v>
+        <v>4.053805405688488</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1181488945658929</v>
+        <v>0.1197038945658929</v>
       </c>
       <c r="C42">
-        <v>159.6364807039338</v>
+        <v>152.9456772361044</v>
       </c>
       <c r="D42">
-        <v>232.3764807039338</v>
+        <v>227.8916772361044</v>
       </c>
       <c r="E42">
-        <v>37.44000000000001</v>
+        <v>39.64600000000002</v>
       </c>
       <c r="F42">
-        <v>88.24000000000001</v>
+        <v>90.44600000000001</v>
       </c>
       <c r="G42">
         <v>15.5</v>
@@ -4731,45 +4731,45 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M42">
-        <v>5.100272000000001</v>
+        <v>5.5443398</v>
       </c>
       <c r="N42">
-        <v>15.57523820408164</v>
+        <v>15.13117040408164</v>
       </c>
       <c r="O42">
         <v>0</v>
       </c>
       <c r="P42">
-        <v>15.57523820408164</v>
+        <v>15.13117040408164</v>
       </c>
       <c r="Q42">
-        <v>23.67523820408163</v>
+        <v>23.23117040408163</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1583814909431548</v>
+        <v>0.1602896518065981</v>
       </c>
       <c r="T42">
-        <v>0.9643487030636537</v>
+        <v>0.9806935963359189</v>
       </c>
       <c r="U42">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V42">
         <v>0</v>
       </c>
       <c r="W42">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y42">
-        <v>4.053805405688488</v>
+        <v>3.729120319083191</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1197038945658929</v>
+        <v>0.1198588945658929</v>
       </c>
       <c r="C43">
-        <v>152.9456772361044</v>
+        <v>150.3021084473737</v>
       </c>
       <c r="D43">
-        <v>227.8916772361044</v>
+        <v>227.4541084473737</v>
       </c>
       <c r="E43">
-        <v>39.64600000000002</v>
+        <v>41.85200000000002</v>
       </c>
       <c r="F43">
-        <v>90.44600000000001</v>
+        <v>92.65200000000002</v>
       </c>
       <c r="G43">
         <v>15.5</v>
@@ -4813,28 +4813,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M43">
-        <v>5.5443398</v>
+        <v>5.679567600000001</v>
       </c>
       <c r="N43">
-        <v>15.13117040408164</v>
+        <v>14.99594260408163</v>
       </c>
       <c r="O43">
         <v>0</v>
       </c>
       <c r="P43">
-        <v>15.13117040408164</v>
+        <v>14.99594260408163</v>
       </c>
       <c r="Q43">
-        <v>23.23117040408163</v>
+        <v>23.09594260408163</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1602896518065981</v>
+        <v>0.162263611320505</v>
       </c>
       <c r="T43">
-        <v>0.9806935963359189</v>
+        <v>0.9976021066175728</v>
       </c>
       <c r="U43">
         <v>0.0613</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.729120319083191</v>
+        <v>3.6403317400574</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1198588945658929</v>
+        <v>0.1200138945658929</v>
       </c>
       <c r="C44">
-        <v>150.3021084473736</v>
+        <v>147.6602167670135</v>
       </c>
       <c r="D44">
-        <v>227.4541084473736</v>
+        <v>227.0182167670135</v>
       </c>
       <c r="E44">
-        <v>41.852</v>
+        <v>44.05800000000001</v>
       </c>
       <c r="F44">
-        <v>92.652</v>
+        <v>94.858</v>
       </c>
       <c r="G44">
         <v>15.5</v>
@@ -4895,28 +4895,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M44">
-        <v>5.6795676</v>
+        <v>5.8147954</v>
       </c>
       <c r="N44">
-        <v>14.99594260408164</v>
+        <v>14.86071480408163</v>
       </c>
       <c r="O44">
         <v>0</v>
       </c>
       <c r="P44">
-        <v>14.99594260408164</v>
+        <v>14.86071480408163</v>
       </c>
       <c r="Q44">
-        <v>23.09594260408164</v>
+        <v>22.96071480408163</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.162263611320505</v>
+        <v>0.1643068325717419</v>
       </c>
       <c r="T44">
-        <v>0.9976021066175726</v>
+        <v>1.015103897961741</v>
       </c>
       <c r="U44">
         <v>0.0613</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.6403317400574</v>
+        <v>3.555672862381647</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1200138945658929</v>
+        <v>0.1214008945658929</v>
       </c>
       <c r="C45">
-        <v>147.6602167670135</v>
+        <v>141.6267992128993</v>
       </c>
       <c r="D45">
-        <v>227.0182167670135</v>
+        <v>223.1907992128993</v>
       </c>
       <c r="E45">
-        <v>44.05800000000001</v>
+        <v>46.26400000000001</v>
       </c>
       <c r="F45">
-        <v>94.858</v>
+        <v>97.06400000000001</v>
       </c>
       <c r="G45">
         <v>15.5</v>
@@ -4977,45 +4977,45 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M45">
-        <v>5.8147954</v>
+        <v>6.221802400000001</v>
       </c>
       <c r="N45">
-        <v>14.86071480408163</v>
+        <v>14.45370780408163</v>
       </c>
       <c r="O45">
         <v>0</v>
       </c>
       <c r="P45">
-        <v>14.86071480408163</v>
+        <v>14.45370780408163</v>
       </c>
       <c r="Q45">
-        <v>22.96071480408163</v>
+        <v>22.55370780408163</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1643068325717419</v>
+        <v>0.166423026010523</v>
       </c>
       <c r="T45">
-        <v>1.015103897961741</v>
+        <v>1.033230753282486</v>
       </c>
       <c r="U45">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V45">
         <v>0</v>
       </c>
       <c r="W45">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y45">
-        <v>3.555672862381647</v>
+        <v>3.32307406678194</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1214008945658929</v>
+        <v>0.1215838945658929</v>
       </c>
       <c r="C46">
-        <v>141.6267992128993</v>
+        <v>138.9254276576101</v>
       </c>
       <c r="D46">
-        <v>223.1907992128993</v>
+        <v>222.6954276576101</v>
       </c>
       <c r="E46">
-        <v>46.26400000000001</v>
+        <v>48.47000000000001</v>
       </c>
       <c r="F46">
-        <v>97.06400000000001</v>
+        <v>99.27000000000001</v>
       </c>
       <c r="G46">
         <v>15.5</v>
@@ -5059,28 +5059,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M46">
-        <v>6.221802400000001</v>
+        <v>6.363207000000001</v>
       </c>
       <c r="N46">
-        <v>14.45370780408163</v>
+        <v>14.31230320408164</v>
       </c>
       <c r="O46">
         <v>0</v>
       </c>
       <c r="P46">
-        <v>14.45370780408163</v>
+        <v>14.31230320408164</v>
       </c>
       <c r="Q46">
-        <v>22.55370780408163</v>
+        <v>22.41230320408163</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.166423026010523</v>
+        <v>0.1686161719379871</v>
       </c>
       <c r="T46">
-        <v>1.033230753282486</v>
+        <v>1.052016766978531</v>
       </c>
       <c r="U46">
         <v>0.0641</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.32307406678194</v>
+        <v>3.249227976409008</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1215838945658929</v>
+        <v>0.1217668945658929</v>
       </c>
       <c r="C47">
-        <v>138.9254276576101</v>
+        <v>136.2262501850121</v>
       </c>
       <c r="D47">
-        <v>222.6954276576101</v>
+        <v>222.2022501850121</v>
       </c>
       <c r="E47">
-        <v>48.47000000000001</v>
+        <v>50.67600000000002</v>
       </c>
       <c r="F47">
-        <v>99.27000000000001</v>
+        <v>101.476</v>
       </c>
       <c r="G47">
         <v>15.5</v>
@@ -5141,28 +5141,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M47">
-        <v>6.363207000000001</v>
+        <v>6.504611600000001</v>
       </c>
       <c r="N47">
-        <v>14.31230320408164</v>
+        <v>14.17089860408164</v>
       </c>
       <c r="O47">
         <v>0</v>
       </c>
       <c r="P47">
-        <v>14.31230320408164</v>
+        <v>14.17089860408164</v>
       </c>
       <c r="Q47">
-        <v>22.41230320408163</v>
+        <v>22.27089860408163</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1686161719379871</v>
+        <v>0.1708905454923942</v>
       </c>
       <c r="T47">
-        <v>1.052016766978531</v>
+        <v>1.071498558959615</v>
       </c>
       <c r="U47">
         <v>0.0641</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.249227976409008</v>
+        <v>3.178592585617507</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1217668945658929</v>
+        <v>0.1219498945658929</v>
       </c>
       <c r="C48">
-        <v>136.2262501850121</v>
+        <v>133.5292522503823</v>
       </c>
       <c r="D48">
-        <v>222.2022501850121</v>
+        <v>221.7112522503823</v>
       </c>
       <c r="E48">
-        <v>50.67600000000002</v>
+        <v>52.88200000000002</v>
       </c>
       <c r="F48">
-        <v>101.476</v>
+        <v>103.682</v>
       </c>
       <c r="G48">
         <v>15.5</v>
@@ -5223,28 +5223,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M48">
-        <v>6.504611600000001</v>
+        <v>6.646016200000002</v>
       </c>
       <c r="N48">
-        <v>14.17089860408164</v>
+        <v>14.02949400408163</v>
       </c>
       <c r="O48">
         <v>0</v>
       </c>
       <c r="P48">
-        <v>14.17089860408164</v>
+        <v>14.02949400408163</v>
       </c>
       <c r="Q48">
-        <v>22.27089860408163</v>
+        <v>22.12949400408163</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1708905454923942</v>
+        <v>0.1732507444639488</v>
       </c>
       <c r="T48">
-        <v>1.071498558959615</v>
+        <v>1.091715512902249</v>
       </c>
       <c r="U48">
         <v>0.0641</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.178592585617507</v>
+        <v>3.110962956136284</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1219498945658929</v>
+        <v>0.1221328945658929</v>
       </c>
       <c r="C49">
-        <v>133.5292522503823</v>
+        <v>130.8344194372714</v>
       </c>
       <c r="D49">
-        <v>221.7112522503823</v>
+        <v>221.2224194372715</v>
       </c>
       <c r="E49">
-        <v>52.88200000000002</v>
+        <v>55.08800000000002</v>
       </c>
       <c r="F49">
-        <v>103.682</v>
+        <v>105.888</v>
       </c>
       <c r="G49">
         <v>15.5</v>
@@ -5305,28 +5305,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M49">
-        <v>6.646016200000002</v>
+        <v>6.787420800000001</v>
       </c>
       <c r="N49">
-        <v>14.02949400408163</v>
+        <v>13.88808940408163</v>
       </c>
       <c r="O49">
         <v>0</v>
       </c>
       <c r="P49">
-        <v>14.02949400408163</v>
+        <v>13.88808940408163</v>
       </c>
       <c r="Q49">
-        <v>22.12949400408163</v>
+        <v>21.98808940408163</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1732507444639488</v>
+        <v>0.1757017203190248</v>
       </c>
       <c r="T49">
-        <v>1.091715512902249</v>
+        <v>1.112710041996523</v>
       </c>
       <c r="U49">
         <v>0.0641</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.110962956136284</v>
+        <v>3.046151227883445</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1221328945658929</v>
+        <v>0.1261378945658929</v>
       </c>
       <c r="C50">
-        <v>130.8344194372715</v>
+        <v>118.4451535709346</v>
       </c>
       <c r="D50">
-        <v>221.2224194372715</v>
+        <v>211.0391535709346</v>
       </c>
       <c r="E50">
-        <v>55.08800000000001</v>
+        <v>57.29400000000001</v>
       </c>
       <c r="F50">
-        <v>105.888</v>
+        <v>108.094</v>
       </c>
       <c r="G50">
         <v>15.5</v>
@@ -5387,45 +5387,45 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M50">
-        <v>6.7874208</v>
+        <v>7.771958600000001</v>
       </c>
       <c r="N50">
-        <v>13.88808940408164</v>
+        <v>12.90355160408163</v>
       </c>
       <c r="O50">
         <v>0</v>
       </c>
       <c r="P50">
-        <v>13.88808940408164</v>
+        <v>12.90355160408163</v>
       </c>
       <c r="Q50">
-        <v>21.98808940408163</v>
+        <v>21.00355160408163</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1757017203190248</v>
+        <v>0.1782488128742998</v>
       </c>
       <c r="T50">
-        <v>1.112710041996523</v>
+        <v>1.13452788595724</v>
       </c>
       <c r="U50">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V50">
         <v>0</v>
       </c>
       <c r="W50">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y50">
-        <v>3.046151227883445</v>
+        <v>2.660270244373359</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1261378945658929</v>
+        <v>0.1263988945658929</v>
       </c>
       <c r="C51">
-        <v>118.4451535709346</v>
+        <v>115.6079664760776</v>
       </c>
       <c r="D51">
-        <v>211.0391535709346</v>
+        <v>210.4079664760777</v>
       </c>
       <c r="E51">
-        <v>57.29400000000001</v>
+        <v>59.50000000000001</v>
       </c>
       <c r="F51">
-        <v>108.094</v>
+        <v>110.3</v>
       </c>
       <c r="G51">
         <v>15.5</v>
@@ -5469,28 +5469,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M51">
-        <v>7.771958600000001</v>
+        <v>7.930570000000001</v>
       </c>
       <c r="N51">
-        <v>12.90355160408163</v>
+        <v>12.74494020408163</v>
       </c>
       <c r="O51">
         <v>0</v>
       </c>
       <c r="P51">
-        <v>12.90355160408163</v>
+        <v>12.74494020408163</v>
       </c>
       <c r="Q51">
-        <v>21.00355160408163</v>
+        <v>20.84494020408163</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1782488128742998</v>
+        <v>0.1808977891317858</v>
       </c>
       <c r="T51">
-        <v>1.13452788595724</v>
+        <v>1.157218443676384</v>
       </c>
       <c r="U51">
         <v>0.07190000000000001</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.660270244373359</v>
+        <v>2.607064839485893</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1263988945658929</v>
+        <v>0.1266598945658929</v>
       </c>
       <c r="C52">
-        <v>115.6079664760776</v>
+        <v>112.7745436983892</v>
       </c>
       <c r="D52">
-        <v>210.4079664760777</v>
+        <v>209.7805436983892</v>
       </c>
       <c r="E52">
-        <v>59.50000000000001</v>
+        <v>61.70600000000002</v>
       </c>
       <c r="F52">
-        <v>110.3</v>
+        <v>112.506</v>
       </c>
       <c r="G52">
         <v>15.5</v>
@@ -5551,28 +5551,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M52">
-        <v>7.930570000000001</v>
+        <v>8.089181400000001</v>
       </c>
       <c r="N52">
-        <v>12.74494020408163</v>
+        <v>12.58632880408164</v>
       </c>
       <c r="O52">
         <v>0</v>
       </c>
       <c r="P52">
-        <v>12.74494020408163</v>
+        <v>12.58632880408164</v>
       </c>
       <c r="Q52">
-        <v>20.84494020408163</v>
+        <v>20.68632880408163</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1808977891317858</v>
+        <v>0.1836548868691692</v>
       </c>
       <c r="T52">
-        <v>1.157218443676384</v>
+        <v>1.180835146608556</v>
       </c>
       <c r="U52">
         <v>0.07190000000000001</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.607064839485893</v>
+        <v>2.5559459210646</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1266598945658929</v>
+        <v>0.1269208945658929</v>
       </c>
       <c r="C53">
-        <v>112.7745436983892</v>
+        <v>109.944851663145</v>
       </c>
       <c r="D53">
-        <v>209.7805436983892</v>
+        <v>209.156851663145</v>
       </c>
       <c r="E53">
-        <v>61.70600000000002</v>
+        <v>63.91200000000002</v>
       </c>
       <c r="F53">
-        <v>112.506</v>
+        <v>114.712</v>
       </c>
       <c r="G53">
         <v>15.5</v>
@@ -5633,28 +5633,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M53">
-        <v>8.089181400000001</v>
+        <v>8.247792800000003</v>
       </c>
       <c r="N53">
-        <v>12.58632880408164</v>
+        <v>12.42771740408163</v>
       </c>
       <c r="O53">
         <v>0</v>
       </c>
       <c r="P53">
-        <v>12.58632880408164</v>
+        <v>12.42771740408163</v>
       </c>
       <c r="Q53">
-        <v>20.68632880408163</v>
+        <v>20.52771740408163</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1836548868691692</v>
+        <v>0.1865268636789435</v>
       </c>
       <c r="T53">
-        <v>1.180835146608556</v>
+        <v>1.205435878829567</v>
       </c>
       <c r="U53">
         <v>0.07190000000000001</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.5559459210646</v>
+        <v>2.50679311489028</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1269208945658929</v>
+        <v>0.1292488945658929</v>
       </c>
       <c r="C54">
-        <v>109.944851663145</v>
+        <v>102.3356296342034</v>
       </c>
       <c r="D54">
-        <v>209.156851663145</v>
+        <v>203.7536296342034</v>
       </c>
       <c r="E54">
-        <v>63.91200000000002</v>
+        <v>66.11800000000002</v>
       </c>
       <c r="F54">
-        <v>114.712</v>
+        <v>116.918</v>
       </c>
       <c r="G54">
         <v>15.5</v>
@@ -5715,45 +5715,45 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M54">
-        <v>8.247792800000003</v>
+        <v>8.862384400000002</v>
       </c>
       <c r="N54">
-        <v>12.42771740408163</v>
+        <v>11.81312580408163</v>
       </c>
       <c r="O54">
         <v>0</v>
       </c>
       <c r="P54">
-        <v>12.42771740408163</v>
+        <v>11.81312580408163</v>
       </c>
       <c r="Q54">
-        <v>20.52771740408163</v>
+        <v>19.91312580408163</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1865268636789435</v>
+        <v>0.1895210522678572</v>
       </c>
       <c r="T54">
-        <v>1.205435878829567</v>
+        <v>1.231083450719558</v>
       </c>
       <c r="U54">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V54">
         <v>0</v>
       </c>
       <c r="W54">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y54">
-        <v>2.50679311489028</v>
+        <v>2.332951186825256</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1292488945658929</v>
+        <v>0.1295488945658929</v>
       </c>
       <c r="C55">
-        <v>102.3356296342034</v>
+        <v>99.45357628574936</v>
       </c>
       <c r="D55">
-        <v>203.7536296342034</v>
+        <v>203.0775762857494</v>
       </c>
       <c r="E55">
-        <v>66.11800000000002</v>
+        <v>68.32400000000003</v>
       </c>
       <c r="F55">
-        <v>116.918</v>
+        <v>119.124</v>
       </c>
       <c r="G55">
         <v>15.5</v>
@@ -5797,28 +5797,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M55">
-        <v>8.862384400000002</v>
+        <v>9.029599200000003</v>
       </c>
       <c r="N55">
-        <v>11.81312580408163</v>
+        <v>11.64591100408163</v>
       </c>
       <c r="O55">
         <v>0</v>
       </c>
       <c r="P55">
-        <v>11.81312580408163</v>
+        <v>11.64591100408163</v>
       </c>
       <c r="Q55">
-        <v>19.91312580408163</v>
+        <v>19.74591100408163</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1895210522678572</v>
+        <v>0.1926454229693324</v>
       </c>
       <c r="T55">
-        <v>1.231083450719558</v>
+        <v>1.257846134430852</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.332951186825256</v>
+        <v>2.289748387069232</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1295488945658929</v>
+        <v>0.1298488945658929</v>
       </c>
       <c r="C56">
-        <v>99.45357628574936</v>
+        <v>96.57599438315667</v>
       </c>
       <c r="D56">
-        <v>203.0775762857494</v>
+        <v>202.4059943831567</v>
       </c>
       <c r="E56">
-        <v>68.32400000000003</v>
+        <v>70.53000000000003</v>
       </c>
       <c r="F56">
-        <v>119.124</v>
+        <v>121.33</v>
       </c>
       <c r="G56">
         <v>15.5</v>
@@ -5879,28 +5879,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M56">
-        <v>9.029599200000003</v>
+        <v>9.196814000000003</v>
       </c>
       <c r="N56">
-        <v>11.64591100408163</v>
+        <v>11.47869620408163</v>
       </c>
       <c r="O56">
         <v>0</v>
       </c>
       <c r="P56">
-        <v>11.64591100408163</v>
+        <v>11.47869620408163</v>
       </c>
       <c r="Q56">
-        <v>19.74591100408163</v>
+        <v>19.57869620408163</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1926454229693324</v>
+        <v>0.1959086545908731</v>
       </c>
       <c r="T56">
-        <v>1.257846134430852</v>
+        <v>1.285798270751538</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.289748387069232</v>
+        <v>2.248116598213428</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1298488945658929</v>
+        <v>0.1301488945658929</v>
       </c>
       <c r="C57">
-        <v>96.57599438315667</v>
+        <v>93.70283971114392</v>
       </c>
       <c r="D57">
-        <v>202.4059943831567</v>
+        <v>201.738839711144</v>
       </c>
       <c r="E57">
-        <v>70.53000000000003</v>
+        <v>72.73600000000003</v>
       </c>
       <c r="F57">
-        <v>121.33</v>
+        <v>123.536</v>
       </c>
       <c r="G57">
         <v>15.5</v>
@@ -5961,28 +5961,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M57">
-        <v>9.196814000000003</v>
+        <v>9.364028800000003</v>
       </c>
       <c r="N57">
-        <v>11.47869620408163</v>
+        <v>11.31148140408163</v>
       </c>
       <c r="O57">
         <v>0</v>
       </c>
       <c r="P57">
-        <v>11.47869620408163</v>
+        <v>11.31148140408163</v>
       </c>
       <c r="Q57">
-        <v>19.57869620408163</v>
+        <v>19.41148140408163</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1959086545908731</v>
+        <v>0.1993202149224839</v>
       </c>
       <c r="T57">
-        <v>1.285798270751538</v>
+        <v>1.315020958723164</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.248116598213428</v>
+        <v>2.207971658959617</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1301488945658929</v>
+        <v>0.1304488945658929</v>
       </c>
       <c r="C58">
-        <v>93.70283971114392</v>
+        <v>90.83406863547033</v>
       </c>
       <c r="D58">
-        <v>201.738839711144</v>
+        <v>201.0760686354704</v>
       </c>
       <c r="E58">
-        <v>72.73600000000003</v>
+        <v>74.94200000000004</v>
       </c>
       <c r="F58">
-        <v>123.536</v>
+        <v>125.742</v>
       </c>
       <c r="G58">
         <v>15.5</v>
@@ -6043,28 +6043,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M58">
-        <v>9.364028800000003</v>
+        <v>9.531243600000003</v>
       </c>
       <c r="N58">
-        <v>11.31148140408163</v>
+        <v>11.14426660408163</v>
       </c>
       <c r="O58">
         <v>0</v>
       </c>
       <c r="P58">
-        <v>11.31148140408163</v>
+        <v>11.14426660408163</v>
       </c>
       <c r="Q58">
-        <v>19.41148140408163</v>
+        <v>19.24426660408163</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1993202149224839</v>
+        <v>0.2028904524788207</v>
       </c>
       <c r="T58">
-        <v>1.315020958723164</v>
+        <v>1.345602841484168</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.207971658959617</v>
+        <v>2.169235314065588</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1304488945658929</v>
+        <v>0.1307488945658929</v>
       </c>
       <c r="C59">
-        <v>90.83406863547033</v>
+        <v>87.9696380934225</v>
       </c>
       <c r="D59">
-        <v>201.0760686354704</v>
+        <v>200.4176380934225</v>
       </c>
       <c r="E59">
-        <v>74.94200000000004</v>
+        <v>77.14800000000004</v>
       </c>
       <c r="F59">
-        <v>125.742</v>
+        <v>127.948</v>
       </c>
       <c r="G59">
         <v>15.5</v>
@@ -6125,28 +6125,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M59">
-        <v>9.531243600000003</v>
+        <v>9.698458400000003</v>
       </c>
       <c r="N59">
-        <v>11.14426660408163</v>
+        <v>10.97705180408163</v>
       </c>
       <c r="O59">
         <v>0</v>
       </c>
       <c r="P59">
-        <v>11.14426660408163</v>
+        <v>10.97705180408163</v>
       </c>
       <c r="Q59">
-        <v>19.24426660408163</v>
+        <v>19.07705180408163</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2028904524788207</v>
+        <v>0.2066307013473641</v>
       </c>
       <c r="T59">
-        <v>1.345602841484168</v>
+        <v>1.377641004376648</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.169235314065588</v>
+        <v>2.131834705202388</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1307488945658929</v>
+        <v>0.1310488945658929</v>
       </c>
       <c r="C60">
-        <v>87.96963809342253</v>
+        <v>85.10950558448712</v>
       </c>
       <c r="D60">
-        <v>200.4176380934225</v>
+        <v>199.7635055844871</v>
       </c>
       <c r="E60">
-        <v>77.14800000000001</v>
+        <v>79.354</v>
       </c>
       <c r="F60">
-        <v>127.948</v>
+        <v>130.154</v>
       </c>
       <c r="G60">
         <v>15.5</v>
@@ -6207,28 +6207,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M60">
-        <v>9.698458400000002</v>
+        <v>9.8656732</v>
       </c>
       <c r="N60">
-        <v>10.97705180408163</v>
+        <v>10.80983700408164</v>
       </c>
       <c r="O60">
         <v>0</v>
       </c>
       <c r="P60">
-        <v>10.97705180408163</v>
+        <v>10.80983700408164</v>
       </c>
       <c r="Q60">
-        <v>19.07705180408163</v>
+        <v>18.90983700408163</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.206630701347364</v>
+        <v>0.2105534013802265</v>
       </c>
       <c r="T60">
-        <v>1.377641004376648</v>
+        <v>1.411242004483395</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.131834705202389</v>
+        <v>2.09570191358879</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1310488945658929</v>
+        <v>0.1313488945658929</v>
       </c>
       <c r="C61">
-        <v>85.10950558448712</v>
+        <v>82.2536291612067</v>
       </c>
       <c r="D61">
-        <v>199.7635055844871</v>
+        <v>199.1136291612067</v>
       </c>
       <c r="E61">
-        <v>79.354</v>
+        <v>81.56000000000002</v>
       </c>
       <c r="F61">
-        <v>130.154</v>
+        <v>132.36</v>
       </c>
       <c r="G61">
         <v>15.5</v>
@@ -6289,28 +6289,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M61">
-        <v>9.8656732</v>
+        <v>10.032888</v>
       </c>
       <c r="N61">
-        <v>10.80983700408164</v>
+        <v>10.64262220408163</v>
       </c>
       <c r="O61">
         <v>0</v>
       </c>
       <c r="P61">
-        <v>10.80983700408164</v>
+        <v>10.64262220408163</v>
       </c>
       <c r="Q61">
-        <v>18.90983700408163</v>
+        <v>18.74262220408163</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2105534013802265</v>
+        <v>0.2146722364147322</v>
       </c>
       <c r="T61">
-        <v>1.411242004483395</v>
+        <v>1.446523054595481</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.09570191358879</v>
+        <v>2.06077354836231</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1313488945658929</v>
+        <v>0.1316488945658929</v>
       </c>
       <c r="C62">
-        <v>82.2536291612067</v>
+        <v>79.4019674202126</v>
       </c>
       <c r="D62">
-        <v>199.1136291612067</v>
+        <v>198.4679674202126</v>
       </c>
       <c r="E62">
-        <v>81.56000000000002</v>
+        <v>83.76600000000001</v>
       </c>
       <c r="F62">
-        <v>132.36</v>
+        <v>134.566</v>
       </c>
       <c r="G62">
         <v>15.5</v>
@@ -6371,28 +6371,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M62">
-        <v>10.032888</v>
+        <v>10.2001028</v>
       </c>
       <c r="N62">
-        <v>10.64262220408163</v>
+        <v>10.47540740408163</v>
       </c>
       <c r="O62">
         <v>0</v>
       </c>
       <c r="P62">
-        <v>10.64262220408163</v>
+        <v>10.47540740408163</v>
       </c>
       <c r="Q62">
-        <v>18.74262220408163</v>
+        <v>18.57540740408163</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2146722364147322</v>
+        <v>0.2190022937586997</v>
       </c>
       <c r="T62">
-        <v>1.446523054595481</v>
+        <v>1.483613389328698</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.06077354836231</v>
+        <v>2.026990375438337</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1316488945658929</v>
+        <v>0.1407528945658929</v>
       </c>
       <c r="C63">
-        <v>79.4019674202126</v>
+        <v>59.41550021074639</v>
       </c>
       <c r="D63">
-        <v>198.4679674202126</v>
+        <v>180.6875002107464</v>
       </c>
       <c r="E63">
-        <v>83.76600000000001</v>
+        <v>85.97200000000002</v>
       </c>
       <c r="F63">
-        <v>134.566</v>
+        <v>136.772</v>
       </c>
       <c r="G63">
         <v>15.5</v>
@@ -6453,45 +6453,45 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M63">
-        <v>10.2001028</v>
+        <v>12.30948</v>
       </c>
       <c r="N63">
-        <v>10.47540740408163</v>
+        <v>8.366030204081635</v>
       </c>
       <c r="O63">
         <v>0</v>
       </c>
       <c r="P63">
-        <v>10.47540740408163</v>
+        <v>8.366030204081635</v>
       </c>
       <c r="Q63">
-        <v>18.57540740408163</v>
+        <v>16.46603020408163</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2190022937586997</v>
+        <v>0.2235602488576129</v>
       </c>
       <c r="T63">
-        <v>1.483613389328698</v>
+        <v>1.522655846942611</v>
       </c>
       <c r="U63">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V63">
         <v>0</v>
       </c>
       <c r="W63">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y63">
-        <v>2.026990375438337</v>
+        <v>1.679641236192076</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1407528945658929</v>
+        <v>0.1411948945658929</v>
       </c>
       <c r="C64">
-        <v>59.41550021074639</v>
+        <v>56.42699724207716</v>
       </c>
       <c r="D64">
-        <v>180.6875002107464</v>
+        <v>179.9049972420772</v>
       </c>
       <c r="E64">
-        <v>85.97200000000002</v>
+        <v>88.17800000000001</v>
       </c>
       <c r="F64">
-        <v>136.772</v>
+        <v>138.978</v>
       </c>
       <c r="G64">
         <v>15.5</v>
@@ -6535,28 +6535,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M64">
-        <v>12.30948</v>
+        <v>12.50802</v>
       </c>
       <c r="N64">
-        <v>8.366030204081635</v>
+        <v>8.167490204081636</v>
       </c>
       <c r="O64">
         <v>0</v>
       </c>
       <c r="P64">
-        <v>8.366030204081635</v>
+        <v>8.167490204081636</v>
       </c>
       <c r="Q64">
-        <v>16.46603020408163</v>
+        <v>16.26749020408163</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2235602488576129</v>
+        <v>0.2283645799078186</v>
       </c>
       <c r="T64">
-        <v>1.522655846942611</v>
+        <v>1.56380870767079</v>
       </c>
       <c r="U64">
         <v>0.09</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>1.679641236192076</v>
+        <v>1.652980264189027</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1411948945658929</v>
+        <v>0.1416368945658929</v>
       </c>
       <c r="C65">
-        <v>56.42699724207716</v>
+        <v>53.44524261622212</v>
       </c>
       <c r="D65">
-        <v>179.9049972420772</v>
+        <v>179.1292426162221</v>
       </c>
       <c r="E65">
-        <v>88.17800000000001</v>
+        <v>90.38400000000003</v>
       </c>
       <c r="F65">
-        <v>138.978</v>
+        <v>141.184</v>
       </c>
       <c r="G65">
         <v>15.5</v>
@@ -6617,28 +6617,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M65">
-        <v>12.50802</v>
+        <v>12.70656</v>
       </c>
       <c r="N65">
-        <v>8.167490204081636</v>
+        <v>7.968950204081635</v>
       </c>
       <c r="O65">
         <v>0</v>
       </c>
       <c r="P65">
-        <v>8.167490204081636</v>
+        <v>7.968950204081635</v>
       </c>
       <c r="Q65">
-        <v>16.26749020408163</v>
+        <v>16.06895020408163</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2283645799078186</v>
+        <v>0.2334358182385914</v>
       </c>
       <c r="T65">
-        <v>1.56380870767079</v>
+        <v>1.607247838439423</v>
       </c>
       <c r="U65">
         <v>0.09</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>1.652980264189027</v>
+        <v>1.627152447561073</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1416368945658929</v>
+        <v>0.1420788945658929</v>
       </c>
       <c r="C66">
-        <v>53.44524261622212</v>
+        <v>50.47014941094807</v>
       </c>
       <c r="D66">
-        <v>179.1292426162221</v>
+        <v>178.3601494109481</v>
       </c>
       <c r="E66">
-        <v>90.38400000000003</v>
+        <v>92.59000000000002</v>
       </c>
       <c r="F66">
-        <v>141.184</v>
+        <v>143.39</v>
       </c>
       <c r="G66">
         <v>15.5</v>
@@ -6699,28 +6699,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M66">
-        <v>12.70656</v>
+        <v>12.9051</v>
       </c>
       <c r="N66">
-        <v>7.968950204081635</v>
+        <v>7.770410204081635</v>
       </c>
       <c r="O66">
         <v>0</v>
       </c>
       <c r="P66">
-        <v>7.968950204081635</v>
+        <v>7.770410204081635</v>
       </c>
       <c r="Q66">
-        <v>16.06895020408163</v>
+        <v>15.87041020408163</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2334358182385914</v>
+        <v>0.2387968416168369</v>
       </c>
       <c r="T66">
-        <v>1.607247838439423</v>
+        <v>1.653169205251978</v>
       </c>
       <c r="U66">
         <v>0.09</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.627152447561073</v>
+        <v>1.602119332983211</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1420788945658929</v>
+        <v>0.1425208945658929</v>
       </c>
       <c r="C67">
-        <v>50.47014941094807</v>
+        <v>47.50163219044555</v>
       </c>
       <c r="D67">
-        <v>178.3601494109481</v>
+        <v>177.5976321904456</v>
       </c>
       <c r="E67">
-        <v>92.59000000000002</v>
+        <v>94.79600000000003</v>
       </c>
       <c r="F67">
-        <v>143.39</v>
+        <v>145.596</v>
       </c>
       <c r="G67">
         <v>15.5</v>
@@ -6781,28 +6781,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M67">
-        <v>12.9051</v>
+        <v>13.10364</v>
       </c>
       <c r="N67">
-        <v>7.770410204081635</v>
+        <v>7.571870204081634</v>
       </c>
       <c r="O67">
         <v>0</v>
       </c>
       <c r="P67">
-        <v>7.770410204081635</v>
+        <v>7.571870204081634</v>
       </c>
       <c r="Q67">
-        <v>15.87041020408163</v>
+        <v>15.67187020408163</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2387968416168369</v>
+        <v>0.2444732193114497</v>
       </c>
       <c r="T67">
-        <v>1.653169205251978</v>
+        <v>1.70179182893586</v>
       </c>
       <c r="U67">
         <v>0.09</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.602119332983211</v>
+        <v>1.57784479763498</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1425208945658929</v>
+        <v>0.1429628945658929</v>
       </c>
       <c r="C68">
-        <v>47.50163219044555</v>
+        <v>44.53960697369106</v>
       </c>
       <c r="D68">
-        <v>177.5976321904456</v>
+        <v>176.8416069736911</v>
       </c>
       <c r="E68">
-        <v>94.79600000000003</v>
+        <v>97.00200000000002</v>
       </c>
       <c r="F68">
-        <v>145.596</v>
+        <v>147.802</v>
       </c>
       <c r="G68">
         <v>15.5</v>
@@ -6863,28 +6863,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M68">
-        <v>13.10364</v>
+        <v>13.30218</v>
       </c>
       <c r="N68">
-        <v>7.571870204081634</v>
+        <v>7.373330204081634</v>
       </c>
       <c r="O68">
         <v>0</v>
       </c>
       <c r="P68">
-        <v>7.571870204081634</v>
+        <v>7.373330204081634</v>
       </c>
       <c r="Q68">
-        <v>15.67187020408163</v>
+        <v>15.47333020408163</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2444732193114497</v>
+        <v>0.2504936198966451</v>
       </c>
       <c r="T68">
-        <v>1.70179182893586</v>
+        <v>1.753361278297552</v>
       </c>
       <c r="U68">
         <v>0.09</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.57784479763498</v>
+        <v>1.554294875282219</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1429628945658929</v>
+        <v>0.1434048945658929</v>
       </c>
       <c r="C69">
-        <v>44.53960697369106</v>
+        <v>41.58399120361324</v>
       </c>
       <c r="D69">
-        <v>176.8416069736911</v>
+        <v>176.0919912036133</v>
       </c>
       <c r="E69">
-        <v>97.00200000000002</v>
+        <v>99.20800000000004</v>
       </c>
       <c r="F69">
-        <v>147.802</v>
+        <v>150.008</v>
       </c>
       <c r="G69">
         <v>15.5</v>
@@ -6945,28 +6945,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M69">
-        <v>13.30218</v>
+        <v>13.50072</v>
       </c>
       <c r="N69">
-        <v>7.373330204081634</v>
+        <v>7.174790204081633</v>
       </c>
       <c r="O69">
         <v>0</v>
       </c>
       <c r="P69">
-        <v>7.373330204081634</v>
+        <v>7.174790204081633</v>
       </c>
       <c r="Q69">
-        <v>15.47333020408163</v>
+        <v>15.27479020408163</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2504936198966451</v>
+        <v>0.2568902955184153</v>
       </c>
       <c r="T69">
-        <v>1.753361278297552</v>
+        <v>1.808153818244351</v>
       </c>
       <c r="U69">
         <v>0.09</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.554294875282219</v>
+        <v>1.53143759770454</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1434048945658929</v>
+        <v>0.1438468945658929</v>
       </c>
       <c r="C70">
-        <v>41.58399120361324</v>
+        <v>38.63470371704028</v>
       </c>
       <c r="D70">
-        <v>176.0919912036133</v>
+        <v>175.3487037170403</v>
       </c>
       <c r="E70">
-        <v>99.20800000000004</v>
+        <v>101.414</v>
       </c>
       <c r="F70">
-        <v>150.008</v>
+        <v>152.214</v>
       </c>
       <c r="G70">
         <v>15.5</v>
@@ -7027,28 +7027,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M70">
-        <v>13.50072</v>
+        <v>13.69926</v>
       </c>
       <c r="N70">
-        <v>7.174790204081633</v>
+        <v>6.976250204081634</v>
       </c>
       <c r="O70">
         <v>0</v>
       </c>
       <c r="P70">
-        <v>7.174790204081633</v>
+        <v>6.976250204081634</v>
       </c>
       <c r="Q70">
-        <v>15.27479020408163</v>
+        <v>15.07625020408163</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2568902955184153</v>
+        <v>0.2636996598899771</v>
       </c>
       <c r="T70">
-        <v>1.808153818244351</v>
+        <v>1.866481360768362</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.53143759770454</v>
+        <v>1.50924284991172</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1438468945658929</v>
+        <v>0.1840488945658929</v>
       </c>
       <c r="C71">
-        <v>38.63470371704028</v>
+        <v>-12.21578713901829</v>
       </c>
       <c r="D71">
-        <v>175.3487037170403</v>
+        <v>126.7042128609818</v>
       </c>
       <c r="E71">
-        <v>101.414</v>
+        <v>103.62</v>
       </c>
       <c r="F71">
-        <v>152.214</v>
+        <v>154.42</v>
       </c>
       <c r="G71">
         <v>15.5</v>
@@ -7109,45 +7109,45 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M71">
-        <v>13.69926</v>
+        <v>22.66885600000001</v>
       </c>
       <c r="N71">
-        <v>6.976250204081634</v>
+        <v>-1.993345795918373</v>
       </c>
       <c r="O71">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P71">
-        <v>6.976250204081634</v>
+        <v>-1.993345795918373</v>
       </c>
       <c r="Q71">
-        <v>15.07625020408163</v>
+        <v>6.106654204081625</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2636996598899771</v>
+        <v>0.2709629818863097</v>
       </c>
       <c r="T71">
-        <v>1.866481360768362</v>
+        <v>1.928697406127308</v>
       </c>
       <c r="U71">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V71">
         <v>0</v>
       </c>
       <c r="W71">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y71">
-        <v>1.50924284991172</v>
+        <v>0.9120667670252803</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1840488945658929</v>
+        <v>0.1850588945658929</v>
       </c>
       <c r="C72">
-        <v>-12.21578713901829</v>
+        <v>-15.29874663212848</v>
       </c>
       <c r="D72">
-        <v>126.7042128609818</v>
+        <v>125.8272533678716</v>
       </c>
       <c r="E72">
-        <v>103.62</v>
+        <v>105.826</v>
       </c>
       <c r="F72">
-        <v>154.42</v>
+        <v>156.626</v>
       </c>
       <c r="G72">
         <v>15.5</v>
@@ -7191,28 +7191,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M72">
-        <v>22.66885600000001</v>
+        <v>22.99269680000001</v>
       </c>
       <c r="N72">
-        <v>-1.993345795918373</v>
+        <v>-2.317186595918372</v>
       </c>
       <c r="O72">
         <v>-0</v>
       </c>
       <c r="P72">
-        <v>-1.993345795918373</v>
+        <v>-2.317186595918372</v>
       </c>
       <c r="Q72">
-        <v>6.106654204081625</v>
+        <v>5.782813404081626</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2709629818863097</v>
+        <v>0.27872722264101</v>
       </c>
       <c r="T72">
-        <v>1.928697406127308</v>
+        <v>1.995204213235146</v>
       </c>
       <c r="U72">
         <v>0.1468</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.9120667670252803</v>
+        <v>0.8992207562221074</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1850588945658929</v>
+        <v>0.1860688945658929</v>
       </c>
       <c r="C73">
-        <v>-15.29874663212846</v>
+        <v>-18.36965014647052</v>
       </c>
       <c r="D73">
-        <v>125.8272533678716</v>
+        <v>124.9623498535295</v>
       </c>
       <c r="E73">
-        <v>105.826</v>
+        <v>108.032</v>
       </c>
       <c r="F73">
-        <v>156.626</v>
+        <v>158.832</v>
       </c>
       <c r="G73">
         <v>15.5</v>
@@ -7273,28 +7273,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M73">
-        <v>22.9926968</v>
+        <v>23.3165376</v>
       </c>
       <c r="N73">
-        <v>-2.317186595918368</v>
+        <v>-2.641027395918368</v>
       </c>
       <c r="O73">
         <v>-0</v>
       </c>
       <c r="P73">
-        <v>-2.317186595918368</v>
+        <v>-2.641027395918368</v>
       </c>
       <c r="Q73">
-        <v>5.782813404081629</v>
+        <v>5.45897260408163</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.27872722264101</v>
+        <v>0.287046052021046</v>
       </c>
       <c r="T73">
-        <v>1.995204213235145</v>
+        <v>2.066461506564972</v>
       </c>
       <c r="U73">
         <v>0.1468</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.8992207562221075</v>
+        <v>0.8867315790523561</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1860688945658929</v>
+        <v>0.1870788945658929</v>
       </c>
       <c r="C74">
-        <v>-18.36965014647052</v>
+        <v>-21.42874459373954</v>
       </c>
       <c r="D74">
-        <v>124.9623498535295</v>
+        <v>124.1092554062605</v>
       </c>
       <c r="E74">
-        <v>108.032</v>
+        <v>110.238</v>
       </c>
       <c r="F74">
-        <v>158.832</v>
+        <v>161.038</v>
       </c>
       <c r="G74">
         <v>15.5</v>
@@ -7355,28 +7355,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M74">
-        <v>23.3165376</v>
+        <v>23.6403784</v>
       </c>
       <c r="N74">
-        <v>-2.641027395918368</v>
+        <v>-2.964868195918367</v>
       </c>
       <c r="O74">
         <v>-0</v>
       </c>
       <c r="P74">
-        <v>-2.641027395918368</v>
+        <v>-2.964868195918367</v>
       </c>
       <c r="Q74">
-        <v>5.45897260408163</v>
+        <v>5.135131804081631</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.287046052021046</v>
+        <v>0.2959810909847885</v>
       </c>
       <c r="T74">
-        <v>2.066461506564972</v>
+        <v>2.14299711791923</v>
       </c>
       <c r="U74">
         <v>0.1468</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.8867315790523561</v>
+        <v>0.8745845711201321</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1870788945658929</v>
+        <v>0.1880888945658929</v>
       </c>
       <c r="C75">
-        <v>-21.42874459373954</v>
+        <v>-24.47627018886962</v>
       </c>
       <c r="D75">
-        <v>124.1092554062605</v>
+        <v>123.2677298111304</v>
       </c>
       <c r="E75">
-        <v>110.238</v>
+        <v>112.444</v>
       </c>
       <c r="F75">
-        <v>161.038</v>
+        <v>163.244</v>
       </c>
       <c r="G75">
         <v>15.5</v>
@@ -7437,28 +7437,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M75">
-        <v>23.6403784</v>
+        <v>23.96421920000001</v>
       </c>
       <c r="N75">
-        <v>-2.964868195918367</v>
+        <v>-3.28870899591837</v>
       </c>
       <c r="O75">
         <v>-0</v>
       </c>
       <c r="P75">
-        <v>-2.964868195918367</v>
+        <v>-3.28870899591837</v>
       </c>
       <c r="Q75">
-        <v>5.135131804081631</v>
+        <v>4.811291004081628</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2959810909847885</v>
+        <v>0.3056034406380496</v>
       </c>
       <c r="T75">
-        <v>2.14299711791923</v>
+        <v>2.225420083993046</v>
       </c>
       <c r="U75">
         <v>0.1468</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.8745845711201321</v>
+        <v>0.8627658606995896</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1880888945658929</v>
+        <v>0.1890988945658929</v>
       </c>
       <c r="C76">
-        <v>-24.47627018886962</v>
+        <v>-27.51246067554203</v>
       </c>
       <c r="D76">
-        <v>123.2677298111304</v>
+        <v>122.437539324458</v>
       </c>
       <c r="E76">
-        <v>112.444</v>
+        <v>114.65</v>
       </c>
       <c r="F76">
-        <v>163.244</v>
+        <v>165.45</v>
       </c>
       <c r="G76">
         <v>15.5</v>
@@ -7519,28 +7519,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M76">
-        <v>23.96421920000001</v>
+        <v>24.28806000000001</v>
       </c>
       <c r="N76">
-        <v>-3.28870899591837</v>
+        <v>-3.612549795918369</v>
       </c>
       <c r="O76">
         <v>-0</v>
       </c>
       <c r="P76">
-        <v>-3.28870899591837</v>
+        <v>-3.612549795918369</v>
       </c>
       <c r="Q76">
-        <v>4.811291004081628</v>
+        <v>4.487450204081629</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3056034406380496</v>
+        <v>0.3159955782635716</v>
       </c>
       <c r="T76">
-        <v>2.225420083993046</v>
+        <v>2.314436887352769</v>
       </c>
       <c r="U76">
         <v>0.1468</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8627658606995896</v>
+        <v>0.8512623158902618</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1890988945658929</v>
+        <v>0.1901088945658929</v>
       </c>
       <c r="C77">
-        <v>-27.51246067554203</v>
+        <v>-30.5375435426426</v>
       </c>
       <c r="D77">
-        <v>122.437539324458</v>
+        <v>121.6184564573574</v>
       </c>
       <c r="E77">
-        <v>114.65</v>
+        <v>116.856</v>
       </c>
       <c r="F77">
-        <v>165.45</v>
+        <v>167.656</v>
       </c>
       <c r="G77">
         <v>15.5</v>
@@ -7601,28 +7601,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M77">
-        <v>24.28806000000001</v>
+        <v>24.6119008</v>
       </c>
       <c r="N77">
-        <v>-3.612549795918369</v>
+        <v>-3.936390595918368</v>
       </c>
       <c r="O77">
         <v>-0</v>
       </c>
       <c r="P77">
-        <v>-3.612549795918369</v>
+        <v>-3.936390595918368</v>
       </c>
       <c r="Q77">
-        <v>4.487450204081629</v>
+        <v>4.16360940408163</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3159955782635716</v>
+        <v>0.327253727357887</v>
       </c>
       <c r="T77">
-        <v>2.314436887352769</v>
+        <v>2.410871757659134</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8512623158902618</v>
+        <v>0.8400614959443373</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1901088945658929</v>
+        <v>0.1911188945658929</v>
       </c>
       <c r="C78">
-        <v>-30.5375435426426</v>
+        <v>-33.55174023208798</v>
       </c>
       <c r="D78">
-        <v>121.6184564573574</v>
+        <v>120.810259767912</v>
       </c>
       <c r="E78">
-        <v>116.856</v>
+        <v>119.062</v>
       </c>
       <c r="F78">
-        <v>167.656</v>
+        <v>169.862</v>
       </c>
       <c r="G78">
         <v>15.5</v>
@@ -7683,28 +7683,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M78">
-        <v>24.6119008</v>
+        <v>24.93574160000001</v>
       </c>
       <c r="N78">
-        <v>-3.936390595918368</v>
+        <v>-4.260231395918371</v>
       </c>
       <c r="O78">
         <v>-0</v>
       </c>
       <c r="P78">
-        <v>-3.936390595918368</v>
+        <v>-4.260231395918371</v>
       </c>
       <c r="Q78">
-        <v>4.16360940408163</v>
+        <v>3.839768604081627</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.327253727357887</v>
+        <v>0.3394908459386647</v>
       </c>
       <c r="T78">
-        <v>2.410871757659134</v>
+        <v>2.515692268861705</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8400614959443373</v>
+        <v>0.8291516063866186</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1911188945658929</v>
+        <v>0.1921288945658929</v>
       </c>
       <c r="C79">
-        <v>-33.55174023208798</v>
+        <v>-36.5552663384203</v>
       </c>
       <c r="D79">
-        <v>120.810259767912</v>
+        <v>120.0127336615797</v>
       </c>
       <c r="E79">
-        <v>119.062</v>
+        <v>121.268</v>
       </c>
       <c r="F79">
-        <v>169.862</v>
+        <v>172.068</v>
       </c>
       <c r="G79">
         <v>15.5</v>
@@ -7765,28 +7765,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M79">
-        <v>24.93574160000001</v>
+        <v>25.2595824</v>
       </c>
       <c r="N79">
-        <v>-4.260231395918371</v>
+        <v>-4.584072195918367</v>
       </c>
       <c r="O79">
         <v>-0</v>
       </c>
       <c r="P79">
-        <v>-4.260231395918371</v>
+        <v>-4.584072195918367</v>
       </c>
       <c r="Q79">
-        <v>3.839768604081627</v>
+        <v>3.515927804081631</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3394908459386647</v>
+        <v>0.3528404298449677</v>
       </c>
       <c r="T79">
-        <v>2.515692268861705</v>
+        <v>2.630041917446329</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8291516063866186</v>
+        <v>0.8185214575867903</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1921288945658929</v>
+        <v>0.1931388945658929</v>
       </c>
       <c r="C80">
-        <v>-36.5552663384203</v>
+        <v>-39.5483318005478</v>
       </c>
       <c r="D80">
-        <v>120.0127336615797</v>
+        <v>119.2256681994522</v>
       </c>
       <c r="E80">
-        <v>121.268</v>
+        <v>123.474</v>
       </c>
       <c r="F80">
-        <v>172.068</v>
+        <v>174.274</v>
       </c>
       <c r="G80">
         <v>15.5</v>
@@ -7847,28 +7847,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M80">
-        <v>25.2595824</v>
+        <v>25.58342320000001</v>
       </c>
       <c r="N80">
-        <v>-4.584072195918367</v>
+        <v>-4.90791299591837</v>
       </c>
       <c r="O80">
         <v>-0</v>
       </c>
       <c r="P80">
-        <v>-4.584072195918367</v>
+        <v>-4.90791299591837</v>
       </c>
       <c r="Q80">
-        <v>3.515927804081631</v>
+        <v>3.192087004081628</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3528404298449677</v>
+        <v>0.3674614026947281</v>
       </c>
       <c r="T80">
-        <v>2.630041917446329</v>
+        <v>2.755282008753297</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8185214575867903</v>
+        <v>0.8081604264780966</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1931388945658929</v>
+        <v>0.2373488945658929</v>
       </c>
       <c r="C81">
-        <v>-39.5483318005478</v>
+        <v>-68.34635691702587</v>
       </c>
       <c r="D81">
-        <v>119.2256681994522</v>
+        <v>92.63364308297415</v>
       </c>
       <c r="E81">
-        <v>123.474</v>
+        <v>125.68</v>
       </c>
       <c r="F81">
-        <v>174.274</v>
+        <v>176.48</v>
       </c>
       <c r="G81">
         <v>15.5</v>
@@ -7929,45 +7929,45 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M81">
-        <v>25.58342320000001</v>
+        <v>35.437184</v>
       </c>
       <c r="N81">
-        <v>-4.90791299591837</v>
+        <v>-14.76167379591837</v>
       </c>
       <c r="O81">
         <v>-0</v>
       </c>
       <c r="P81">
-        <v>-4.90791299591837</v>
+        <v>-14.76167379591837</v>
       </c>
       <c r="Q81">
-        <v>3.192087004081628</v>
+        <v>-6.661673795918368</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3674614026947281</v>
+        <v>0.3835444728294645</v>
       </c>
       <c r="T81">
-        <v>2.755282008753297</v>
+        <v>2.893046109190962</v>
       </c>
       <c r="U81">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V81">
         <v>0</v>
       </c>
       <c r="W81">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y81">
-        <v>0.8081604264780966</v>
+        <v>0.583441116655365</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2373488945658929</v>
+        <v>0.2388988945658929</v>
       </c>
       <c r="C82">
-        <v>-68.34635691702587</v>
+        <v>-71.27110832780741</v>
       </c>
       <c r="D82">
-        <v>92.63364308297415</v>
+        <v>91.91489167219262</v>
       </c>
       <c r="E82">
-        <v>125.68</v>
+        <v>127.886</v>
       </c>
       <c r="F82">
-        <v>176.48</v>
+        <v>178.686</v>
       </c>
       <c r="G82">
         <v>15.5</v>
@@ -8011,28 +8011,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M82">
-        <v>35.437184</v>
+        <v>35.88014880000001</v>
       </c>
       <c r="N82">
-        <v>-14.76167379591837</v>
+        <v>-15.20463859591837</v>
       </c>
       <c r="O82">
         <v>-0</v>
       </c>
       <c r="P82">
-        <v>-14.76167379591837</v>
+        <v>-15.20463859591837</v>
       </c>
       <c r="Q82">
-        <v>-6.661673795918368</v>
+        <v>-7.104638595918374</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3835444728294645</v>
+        <v>0.4013204977152259</v>
       </c>
       <c r="T82">
-        <v>2.893046109190962</v>
+        <v>3.045311693885223</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.583441116655365</v>
+        <v>0.5762381399065333</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2388988945658929</v>
+        <v>0.2404488945658929</v>
       </c>
       <c r="C83">
-        <v>-71.27110832780741</v>
+        <v>-74.18479192199352</v>
       </c>
       <c r="D83">
-        <v>91.91489167219262</v>
+        <v>91.2072080780065</v>
       </c>
       <c r="E83">
-        <v>127.886</v>
+        <v>130.092</v>
       </c>
       <c r="F83">
-        <v>178.686</v>
+        <v>180.892</v>
       </c>
       <c r="G83">
         <v>15.5</v>
@@ -8093,28 +8093,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M83">
-        <v>35.88014880000001</v>
+        <v>36.32311360000001</v>
       </c>
       <c r="N83">
-        <v>-15.20463859591837</v>
+        <v>-15.64760339591837</v>
       </c>
       <c r="O83">
         <v>-0</v>
       </c>
       <c r="P83">
-        <v>-15.20463859591837</v>
+        <v>-15.64760339591837</v>
       </c>
       <c r="Q83">
-        <v>-7.104638595918374</v>
+        <v>-7.547603395918372</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4013204977152259</v>
+        <v>0.4210716364771829</v>
       </c>
       <c r="T83">
-        <v>3.045311693885223</v>
+        <v>3.214495676878847</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.5762381399065333</v>
+        <v>0.5692108455174292</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2404488945658929</v>
+        <v>0.2419988945658929</v>
       </c>
       <c r="C84">
-        <v>-74.18479192199352</v>
+        <v>-77.08766139083194</v>
       </c>
       <c r="D84">
-        <v>91.2072080780065</v>
+        <v>90.5103386091681</v>
       </c>
       <c r="E84">
-        <v>130.092</v>
+        <v>132.2980000000001</v>
       </c>
       <c r="F84">
-        <v>180.892</v>
+        <v>183.098</v>
       </c>
       <c r="G84">
         <v>15.5</v>
@@ -8175,28 +8175,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M84">
-        <v>36.32311360000001</v>
+        <v>36.76607840000001</v>
       </c>
       <c r="N84">
-        <v>-15.64760339591837</v>
+        <v>-16.09056819591838</v>
       </c>
       <c r="O84">
         <v>-0</v>
       </c>
       <c r="P84">
-        <v>-15.64760339591837</v>
+        <v>-16.09056819591838</v>
       </c>
       <c r="Q84">
-        <v>-7.547603395918372</v>
+        <v>-7.990568195918378</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4210716364771829</v>
+        <v>0.4431464386228995</v>
       </c>
       <c r="T84">
-        <v>3.214495676878847</v>
+        <v>3.40358365787172</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.5692108455174292</v>
+        <v>0.5623528835232432</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2419988945658929</v>
+        <v>0.2435488945658929</v>
       </c>
       <c r="C85">
-        <v>-77.08766139083194</v>
+        <v>-79.97996273103963</v>
       </c>
       <c r="D85">
-        <v>90.5103386091681</v>
+        <v>89.8240372689604</v>
       </c>
       <c r="E85">
-        <v>132.2980000000001</v>
+        <v>134.504</v>
       </c>
       <c r="F85">
-        <v>183.098</v>
+        <v>185.304</v>
       </c>
       <c r="G85">
         <v>15.5</v>
@@ -8257,28 +8257,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M85">
-        <v>36.76607840000001</v>
+        <v>37.20904320000001</v>
       </c>
       <c r="N85">
-        <v>-16.09056819591838</v>
+        <v>-16.53353299591837</v>
       </c>
       <c r="O85">
         <v>-0</v>
       </c>
       <c r="P85">
-        <v>-16.09056819591838</v>
+        <v>-16.53353299591837</v>
       </c>
       <c r="Q85">
-        <v>-7.990568195918378</v>
+        <v>-8.433532995918377</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4431464386228995</v>
+        <v>0.4679805910368308</v>
       </c>
       <c r="T85">
-        <v>3.40358365787172</v>
+        <v>3.616307636488703</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5623528835232432</v>
+        <v>0.5556582063384428</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2435488945658929</v>
+        <v>0.2450988945658929</v>
       </c>
       <c r="C86">
-        <v>-79.97996273103961</v>
+        <v>-82.86193453432948</v>
       </c>
       <c r="D86">
-        <v>89.8240372689604</v>
+        <v>89.14806546567054</v>
       </c>
       <c r="E86">
-        <v>134.504</v>
+        <v>136.71</v>
       </c>
       <c r="F86">
-        <v>185.304</v>
+        <v>187.51</v>
       </c>
       <c r="G86">
         <v>15.5</v>
@@ -8339,28 +8339,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M86">
-        <v>37.2090432</v>
+        <v>37.652008</v>
       </c>
       <c r="N86">
-        <v>-16.53353299591837</v>
+        <v>-16.97649779591837</v>
       </c>
       <c r="O86">
         <v>-0</v>
       </c>
       <c r="P86">
-        <v>-16.53353299591837</v>
+        <v>-16.97649779591837</v>
       </c>
       <c r="Q86">
-        <v>-8.43353299591837</v>
+        <v>-8.876497795918368</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4679805910368305</v>
+        <v>0.4961259637726192</v>
       </c>
       <c r="T86">
-        <v>3.616307636488701</v>
+        <v>3.857394812254614</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.5556582063384429</v>
+        <v>0.5491210509697553</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2450988945658929</v>
+        <v>0.2466488945658929</v>
       </c>
       <c r="C87">
-        <v>-82.86193453432948</v>
+        <v>-85.73380826396105</v>
       </c>
       <c r="D87">
-        <v>89.14806546567054</v>
+        <v>88.48219173603896</v>
       </c>
       <c r="E87">
-        <v>136.71</v>
+        <v>138.916</v>
       </c>
       <c r="F87">
-        <v>187.51</v>
+        <v>189.716</v>
       </c>
       <c r="G87">
         <v>15.5</v>
@@ -8421,28 +8421,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M87">
-        <v>37.652008</v>
+        <v>38.0949728</v>
       </c>
       <c r="N87">
-        <v>-16.97649779591837</v>
+        <v>-17.41946259591836</v>
       </c>
       <c r="O87">
         <v>-0</v>
       </c>
       <c r="P87">
-        <v>-16.97649779591837</v>
+        <v>-17.41946259591836</v>
       </c>
       <c r="Q87">
-        <v>-8.876497795918368</v>
+        <v>-9.319462595918367</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4961259637726192</v>
+        <v>0.528292104042092</v>
       </c>
       <c r="T87">
-        <v>3.857394812254614</v>
+        <v>4.132923013129944</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5491210509697553</v>
+        <v>0.542735922470107</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2466488945658929</v>
+        <v>0.2481988945658929</v>
       </c>
       <c r="C88">
-        <v>-85.73380826396105</v>
+        <v>-88.5958085189898</v>
       </c>
       <c r="D88">
-        <v>88.48219173603896</v>
+        <v>87.82619148101023</v>
       </c>
       <c r="E88">
-        <v>138.916</v>
+        <v>141.122</v>
       </c>
       <c r="F88">
-        <v>189.716</v>
+        <v>191.922</v>
       </c>
       <c r="G88">
         <v>15.5</v>
@@ -8503,28 +8503,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M88">
-        <v>38.0949728</v>
+        <v>38.53793760000001</v>
       </c>
       <c r="N88">
-        <v>-17.41946259591836</v>
+        <v>-17.86242739591837</v>
       </c>
       <c r="O88">
         <v>-0</v>
       </c>
       <c r="P88">
-        <v>-17.41946259591836</v>
+        <v>-17.86242739591837</v>
       </c>
       <c r="Q88">
-        <v>-9.319462595918367</v>
+        <v>-9.762427395918372</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.528292104042092</v>
+        <v>0.5654068812760991</v>
       </c>
       <c r="T88">
-        <v>4.132923013129944</v>
+        <v>4.450840167986093</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.542735922470107</v>
+        <v>0.536497578533669</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2481988945658929</v>
+        <v>0.2497488945658929</v>
       </c>
       <c r="C89">
-        <v>-88.5958085189898</v>
+        <v>-91.44815328684776</v>
       </c>
       <c r="D89">
-        <v>87.82619148101023</v>
+        <v>87.17984671315226</v>
       </c>
       <c r="E89">
-        <v>141.122</v>
+        <v>143.328</v>
       </c>
       <c r="F89">
-        <v>191.922</v>
+        <v>194.128</v>
       </c>
       <c r="G89">
         <v>15.5</v>
@@ -8585,28 +8585,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M89">
-        <v>38.53793760000001</v>
+        <v>38.98090240000001</v>
       </c>
       <c r="N89">
-        <v>-17.86242739591837</v>
+        <v>-18.30539219591837</v>
       </c>
       <c r="O89">
         <v>-0</v>
       </c>
       <c r="P89">
-        <v>-17.86242739591837</v>
+        <v>-18.30539219591837</v>
       </c>
       <c r="Q89">
-        <v>-9.762427395918372</v>
+        <v>-10.20539219591837</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5654068812760991</v>
+        <v>0.608707454715774</v>
       </c>
       <c r="T89">
-        <v>4.450840167986093</v>
+        <v>4.821743515318269</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.536497578533669</v>
+        <v>0.5304010151412408</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2497488945658929</v>
+        <v>0.2512988945658929</v>
       </c>
       <c r="C90">
-        <v>-91.44815328684776</v>
+        <v>-94.29105418485301</v>
       </c>
       <c r="D90">
-        <v>87.17984671315226</v>
+        <v>86.54294581514702</v>
       </c>
       <c r="E90">
-        <v>143.328</v>
+        <v>145.534</v>
       </c>
       <c r="F90">
-        <v>194.128</v>
+        <v>196.334</v>
       </c>
       <c r="G90">
         <v>15.5</v>
@@ -8667,28 +8667,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M90">
-        <v>38.98090240000001</v>
+        <v>39.42386720000001</v>
       </c>
       <c r="N90">
-        <v>-18.30539219591837</v>
+        <v>-18.74835699591837</v>
       </c>
       <c r="O90">
         <v>-0</v>
       </c>
       <c r="P90">
-        <v>-18.30539219591837</v>
+        <v>-18.74835699591837</v>
       </c>
       <c r="Q90">
-        <v>-10.20539219591837</v>
+        <v>-10.64835699591838</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.608707454715774</v>
+        <v>0.6598808596899354</v>
       </c>
       <c r="T90">
-        <v>4.821743515318269</v>
+        <v>5.260083834892657</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5304010151412408</v>
+        <v>0.5244414531733617</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2512988945658929</v>
+        <v>0.2528488945658929</v>
       </c>
       <c r="C91">
-        <v>-94.29105418485301</v>
+        <v>-97.12471669120937</v>
       </c>
       <c r="D91">
-        <v>86.54294581514702</v>
+        <v>85.91528330879065</v>
       </c>
       <c r="E91">
-        <v>145.534</v>
+        <v>147.74</v>
       </c>
       <c r="F91">
-        <v>196.334</v>
+        <v>198.54</v>
       </c>
       <c r="G91">
         <v>15.5</v>
@@ -8749,28 +8749,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M91">
-        <v>39.42386720000001</v>
+        <v>39.866832</v>
       </c>
       <c r="N91">
-        <v>-18.74835699591837</v>
+        <v>-19.19132179591837</v>
       </c>
       <c r="O91">
         <v>-0</v>
       </c>
       <c r="P91">
-        <v>-18.74835699591837</v>
+        <v>-19.19132179591837</v>
       </c>
       <c r="Q91">
-        <v>-10.64835699591838</v>
+        <v>-11.09132179591837</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6598808596899354</v>
+        <v>0.721288945658929</v>
       </c>
       <c r="T91">
-        <v>5.260083834892657</v>
+        <v>5.786092218381923</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5244414531733617</v>
+        <v>0.51861432591588</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2528488945658929</v>
+        <v>0.2543988945658929</v>
       </c>
       <c r="C92">
-        <v>-97.12471669120937</v>
+        <v>-99.94934036602679</v>
       </c>
       <c r="D92">
-        <v>85.91528330879065</v>
+        <v>85.29665963397325</v>
       </c>
       <c r="E92">
-        <v>147.74</v>
+        <v>149.946</v>
       </c>
       <c r="F92">
-        <v>198.54</v>
+        <v>200.746</v>
       </c>
       <c r="G92">
         <v>15.5</v>
@@ -8831,28 +8831,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M92">
-        <v>39.866832</v>
+        <v>40.30979680000001</v>
       </c>
       <c r="N92">
-        <v>-19.19132179591837</v>
+        <v>-19.63428659591837</v>
       </c>
       <c r="O92">
         <v>-0</v>
       </c>
       <c r="P92">
-        <v>-19.19132179591837</v>
+        <v>-19.63428659591837</v>
       </c>
       <c r="Q92">
-        <v>-11.09132179591837</v>
+        <v>-11.53428659591837</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.721288945658929</v>
+        <v>0.7963432729543657</v>
       </c>
       <c r="T92">
-        <v>5.786092218381923</v>
+        <v>6.428991353757693</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.51861432591588</v>
+        <v>0.5129152673893318</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2543988945658929</v>
+        <v>0.2559488945658929</v>
       </c>
       <c r="C93">
-        <v>-99.94934036602679</v>
+        <v>-102.7651190628607</v>
       </c>
       <c r="D93">
-        <v>85.29665963397325</v>
+        <v>84.68688093713928</v>
       </c>
       <c r="E93">
-        <v>149.946</v>
+        <v>152.152</v>
       </c>
       <c r="F93">
-        <v>200.746</v>
+        <v>202.952</v>
       </c>
       <c r="G93">
         <v>15.5</v>
@@ -8913,28 +8913,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M93">
-        <v>40.30979680000001</v>
+        <v>40.75276160000001</v>
       </c>
       <c r="N93">
-        <v>-19.63428659591837</v>
+        <v>-20.07725139591837</v>
       </c>
       <c r="O93">
         <v>-0</v>
       </c>
       <c r="P93">
-        <v>-19.63428659591837</v>
+        <v>-20.07725139591837</v>
       </c>
       <c r="Q93">
-        <v>-11.53428659591837</v>
+        <v>-11.97725139591837</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7963432729543657</v>
+        <v>0.8901611820736616</v>
       </c>
       <c r="T93">
-        <v>6.428991353757693</v>
+        <v>7.232615272977407</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5129152673893318</v>
+        <v>0.5073401014394479</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2559488945658929</v>
+        <v>0.2574988945658929</v>
       </c>
       <c r="C94">
-        <v>-102.7651190628607</v>
+        <v>-105.5722411312432</v>
       </c>
       <c r="D94">
-        <v>84.68688093713928</v>
+        <v>84.08575886875684</v>
       </c>
       <c r="E94">
-        <v>152.152</v>
+        <v>154.3580000000001</v>
       </c>
       <c r="F94">
-        <v>202.952</v>
+        <v>205.158</v>
       </c>
       <c r="G94">
         <v>15.5</v>
@@ -8995,28 +8995,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M94">
-        <v>40.75276160000001</v>
+        <v>41.19572640000001</v>
       </c>
       <c r="N94">
-        <v>-20.07725139591837</v>
+        <v>-20.52021619591838</v>
       </c>
       <c r="O94">
         <v>-0</v>
       </c>
       <c r="P94">
-        <v>-20.07725139591837</v>
+        <v>-20.52021619591838</v>
       </c>
       <c r="Q94">
-        <v>-11.97725139591837</v>
+        <v>-12.42021619591838</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.8901611820736616</v>
+        <v>1.010784208084185</v>
       </c>
       <c r="T94">
-        <v>7.232615272977407</v>
+        <v>8.265846026259894</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5073401014394479</v>
+        <v>0.5018848315314967</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2574988945658929</v>
+        <v>0.2919488945658929</v>
       </c>
       <c r="C95">
-        <v>-105.5722411312432</v>
+        <v>-119.2361929889583</v>
       </c>
       <c r="D95">
-        <v>84.08575886875684</v>
+        <v>72.62780701104174</v>
       </c>
       <c r="E95">
-        <v>154.3580000000001</v>
+        <v>156.564</v>
       </c>
       <c r="F95">
-        <v>205.158</v>
+        <v>207.364</v>
       </c>
       <c r="G95">
         <v>15.5</v>
@@ -9077,45 +9077,45 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M95">
-        <v>41.19572640000001</v>
+        <v>48.89643120000001</v>
       </c>
       <c r="N95">
-        <v>-20.52021619591838</v>
+        <v>-28.22092099591837</v>
       </c>
       <c r="O95">
         <v>-0</v>
       </c>
       <c r="P95">
-        <v>-20.52021619591838</v>
+        <v>-28.22092099591837</v>
       </c>
       <c r="Q95">
-        <v>-12.42021619591838</v>
+        <v>-20.12092099591838</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.010784208084185</v>
+        <v>1.171614909431549</v>
       </c>
       <c r="T95">
-        <v>8.265846026259894</v>
+        <v>9.643487030636546</v>
       </c>
       <c r="U95">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V95">
         <v>0</v>
       </c>
       <c r="W95">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y95">
-        <v>0.5018848315314967</v>
+        <v>0.4228429293645797</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2919488945658929</v>
+        <v>0.2938488945658929</v>
       </c>
       <c r="C96">
-        <v>-119.2361929889583</v>
+        <v>-121.9839445624186</v>
       </c>
       <c r="D96">
-        <v>72.62780701104174</v>
+        <v>72.08605543758149</v>
       </c>
       <c r="E96">
-        <v>156.564</v>
+        <v>158.77</v>
       </c>
       <c r="F96">
-        <v>207.364</v>
+        <v>209.5700000000001</v>
       </c>
       <c r="G96">
         <v>15.5</v>
@@ -9159,28 +9159,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M96">
-        <v>48.89643120000001</v>
+        <v>49.41660600000002</v>
       </c>
       <c r="N96">
-        <v>-28.22092099591837</v>
+        <v>-28.74109579591838</v>
       </c>
       <c r="O96">
         <v>-0</v>
       </c>
       <c r="P96">
-        <v>-28.22092099591837</v>
+        <v>-28.74109579591838</v>
       </c>
       <c r="Q96">
-        <v>-20.12092099591838</v>
+        <v>-20.64109579591838</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.171614909431549</v>
+        <v>1.39677789131786</v>
       </c>
       <c r="T96">
-        <v>9.643487030636546</v>
+        <v>11.57218443676386</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.4228429293645797</v>
+        <v>0.418391951160742</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2938488945658929</v>
+        <v>0.2957488945658929</v>
       </c>
       <c r="C97">
-        <v>-121.9839445624186</v>
+        <v>-124.723673816952</v>
       </c>
       <c r="D97">
-        <v>72.08605543758149</v>
+        <v>71.552326183048</v>
       </c>
       <c r="E97">
-        <v>158.77</v>
+        <v>160.9760000000001</v>
       </c>
       <c r="F97">
-        <v>209.5700000000001</v>
+        <v>211.776</v>
       </c>
       <c r="G97">
         <v>15.5</v>
@@ -9241,28 +9241,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M97">
-        <v>49.41660600000002</v>
+        <v>49.93678080000001</v>
       </c>
       <c r="N97">
-        <v>-28.74109579591838</v>
+        <v>-29.26127059591837</v>
       </c>
       <c r="O97">
         <v>-0</v>
       </c>
       <c r="P97">
-        <v>-28.74109579591838</v>
+        <v>-29.26127059591837</v>
       </c>
       <c r="Q97">
-        <v>-20.64109579591838</v>
+        <v>-21.16127059591837</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.39677789131786</v>
+        <v>1.734522364147326</v>
       </c>
       <c r="T97">
-        <v>11.57218443676386</v>
+        <v>14.46523054595483</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.418391951160742</v>
+        <v>0.4140337016694843</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2957488945658929</v>
+        <v>0.2976488945658929</v>
       </c>
       <c r="C98">
-        <v>-124.723673816952</v>
+        <v>-127.4555576360204</v>
       </c>
       <c r="D98">
-        <v>71.552326183048</v>
+        <v>71.02644236397958</v>
       </c>
       <c r="E98">
-        <v>160.976</v>
+        <v>163.182</v>
       </c>
       <c r="F98">
-        <v>211.776</v>
+        <v>213.982</v>
       </c>
       <c r="G98">
         <v>15.5</v>
@@ -9323,28 +9323,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M98">
-        <v>49.9367808</v>
+        <v>50.45695560000001</v>
       </c>
       <c r="N98">
-        <v>-29.26127059591836</v>
+        <v>-29.78144539591837</v>
       </c>
       <c r="O98">
         <v>-0</v>
       </c>
       <c r="P98">
-        <v>-29.26127059591836</v>
+        <v>-29.78144539591837</v>
       </c>
       <c r="Q98">
-        <v>-21.16127059591837</v>
+        <v>-21.68144539591837</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.734522364147321</v>
+        <v>2.297429818863094</v>
       </c>
       <c r="T98">
-        <v>14.46523054595479</v>
+        <v>19.28697406127306</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.4140337016694844</v>
+        <v>0.4097653129924793</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2976488945658929</v>
+        <v>0.2995488945658929</v>
       </c>
       <c r="C99">
-        <v>-127.4555576360204</v>
+        <v>-130.1797677409067</v>
       </c>
       <c r="D99">
-        <v>71.02644236397958</v>
+        <v>70.50823225909329</v>
       </c>
       <c r="E99">
-        <v>163.182</v>
+        <v>165.388</v>
       </c>
       <c r="F99">
-        <v>213.982</v>
+        <v>216.188</v>
       </c>
       <c r="G99">
         <v>15.5</v>
@@ -9405,28 +9405,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M99">
-        <v>50.45695560000001</v>
+        <v>50.97713040000001</v>
       </c>
       <c r="N99">
-        <v>-29.78144539591837</v>
+        <v>-30.30162019591837</v>
       </c>
       <c r="O99">
         <v>-0</v>
       </c>
       <c r="P99">
-        <v>-29.78144539591837</v>
+        <v>-30.30162019591837</v>
       </c>
       <c r="Q99">
-        <v>-21.68144539591837</v>
+        <v>-22.20162019591837</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.297429818863094</v>
+        <v>3.423244728294641</v>
       </c>
       <c r="T99">
-        <v>19.28697406127306</v>
+        <v>28.93046109190959</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.4097653129924793</v>
+        <v>0.4055840342884744</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2995488945658929</v>
+        <v>0.3014488945658929</v>
       </c>
       <c r="C100">
-        <v>-130.1797677409067</v>
+        <v>-132.8964708776679</v>
       </c>
       <c r="D100">
-        <v>70.50823225909329</v>
+        <v>69.99752912233218</v>
       </c>
       <c r="E100">
-        <v>165.388</v>
+        <v>167.5940000000001</v>
       </c>
       <c r="F100">
-        <v>216.188</v>
+        <v>218.394</v>
       </c>
       <c r="G100">
         <v>15.5</v>
@@ -9487,28 +9487,28 @@
         <v>20.67551020408164</v>
       </c>
       <c r="M100">
-        <v>50.97713040000001</v>
+        <v>51.49730520000001</v>
       </c>
       <c r="N100">
-        <v>-30.30162019591837</v>
+        <v>-30.82179499591837</v>
       </c>
       <c r="O100">
         <v>-0</v>
       </c>
       <c r="P100">
-        <v>-30.30162019591837</v>
+        <v>-30.82179499591837</v>
       </c>
       <c r="Q100">
-        <v>-22.20162019591837</v>
+        <v>-22.72179499591837</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.423244728294641</v>
+        <v>6.800689456589283</v>
       </c>
       <c r="T100">
-        <v>28.93046109190959</v>
+        <v>57.86092218381917</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.4055840342884744</v>
+        <v>0.4014872258613181</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3014488945658929</v>
-      </c>
-      <c r="C101">
-        <v>-132.8964708776679</v>
-      </c>
-      <c r="D101">
-        <v>69.99752912233218</v>
-      </c>
-      <c r="E101">
-        <v>167.5940000000001</v>
-      </c>
-      <c r="F101">
-        <v>218.394</v>
-      </c>
-      <c r="G101">
-        <v>15.5</v>
-      </c>
-      <c r="H101">
-        <v>169.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>28.77551020408163</v>
-      </c>
-      <c r="K101">
-        <v>8.099999999999998</v>
-      </c>
-      <c r="L101">
-        <v>20.67551020408164</v>
-      </c>
-      <c r="M101">
-        <v>51.49730520000001</v>
-      </c>
-      <c r="N101">
-        <v>-30.82179499591837</v>
-      </c>
-      <c r="O101">
-        <v>-0</v>
-      </c>
-      <c r="P101">
-        <v>-30.82179499591837</v>
-      </c>
-      <c r="Q101">
-        <v>-22.72179499591837</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.800689456589283</v>
-      </c>
-      <c r="T101">
-        <v>57.86092218381917</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0</v>
-      </c>
-      <c r="W101">
-        <v>0.2358</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.4014872258613181</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
